--- a/datos.xlsx
+++ b/datos.xlsx
@@ -449,11 +449,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -626,55 +626,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
+          <t>STENT BARE DES (SE21)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SE32001</t>
+          <t>SE21029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2-2,50 x 9</t>
+          <t>2,75-3,50 x 19</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>476</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IVOLUTION</t>
+          <t>ANGIOLITE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STENT IVOLUTIO</t>
+          <t>STENT BARE DES (SE21)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SE24220</t>
+          <t>SE21029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6 x 200</t>
+          <t>2,75-3,50 x 19</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>476</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -686,25 +686,385 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
+          <t>STENT BARE DES (SE21)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SE32005</t>
+          <t>SE21031</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 14</t>
+          <t>2,00-2,5 x 24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>S21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SE21031</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 24</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SE21032</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2,75-3,5 x 24</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>247</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>243</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>243</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>243</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>S23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>243</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>243</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SE21040</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 39</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>243</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SE21034</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2,00-2,5 x 29</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SE21041</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2,75-3,5 x 39</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>194</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SE21041</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2,75-3,5 x 39</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>194</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ANGIOLITE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>STENT BARE DES (SE21)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SE21041</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2,75-3,5 x 39</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>194</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -6752,11 +7112,11 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -8019,25 +8379,25 @@
         <v>199</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F34" t="n">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="H34" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="I34" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="J34" t="n">
-        <v>334</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>334</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -8058,25 +8418,25 @@
         <v>399</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>-94</v>
       </c>
       <c r="G35" t="n">
-        <v>52</v>
+        <v>-91</v>
       </c>
       <c r="H35" t="n">
-        <v>52</v>
+        <v>-91</v>
       </c>
       <c r="I35" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="J35" t="n">
-        <v>251</v>
+        <v>109</v>
       </c>
       <c r="K35" t="n">
-        <v>251</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36">
@@ -8100,22 +8460,22 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="G36" t="n">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="H36" t="n">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="I36" t="n">
-        <v>176</v>
+        <v>627</v>
       </c>
       <c r="J36" t="n">
-        <v>375</v>
+        <v>627</v>
       </c>
       <c r="K36" t="n">
-        <v>375</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37">
@@ -8136,25 +8496,25 @@
         <v>800</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>-44</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>-44</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>156</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>-36</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>-32</v>
       </c>
       <c r="K37" t="n">
-        <v>204</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="38">
@@ -8175,25 +8535,25 @@
         <v>550</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F38" t="n">
-        <v>546</v>
+        <v>-42</v>
       </c>
       <c r="G38" t="n">
-        <v>546</v>
+        <v>108</v>
       </c>
       <c r="H38" t="n">
-        <v>546</v>
+        <v>108</v>
       </c>
       <c r="I38" t="n">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="J38" t="n">
-        <v>696</v>
+        <v>508</v>
       </c>
       <c r="K38" t="n">
-        <v>696</v>
+        <v>508</v>
       </c>
     </row>
     <row r="39">
@@ -8214,25 +8574,25 @@
         <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F39" t="n">
-        <v>545</v>
+        <v>153</v>
       </c>
       <c r="G39" t="n">
-        <v>545</v>
+        <v>55</v>
       </c>
       <c r="H39" t="n">
-        <v>545</v>
+        <v>55</v>
       </c>
       <c r="I39" t="n">
-        <v>545</v>
+        <v>255</v>
       </c>
       <c r="J39" t="n">
-        <v>545</v>
+        <v>255</v>
       </c>
       <c r="K39" t="n">
-        <v>545</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40">
@@ -8253,25 +8613,25 @@
         <v>800</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>-190</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>-190</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>-182</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>-178</v>
       </c>
       <c r="K40" t="n">
-        <v>206</v>
+        <v>-174</v>
       </c>
     </row>
     <row r="41">
@@ -8295,22 +8655,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>406</v>
+        <v>-476</v>
       </c>
       <c r="G41" t="n">
-        <v>406</v>
+        <v>-476</v>
       </c>
       <c r="H41" t="n">
-        <v>406</v>
+        <v>224</v>
       </c>
       <c r="I41" t="n">
-        <v>406</v>
+        <v>224</v>
       </c>
       <c r="J41" t="n">
-        <v>406</v>
+        <v>224</v>
       </c>
       <c r="K41" t="n">
-        <v>1106</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42">
@@ -8331,25 +8691,25 @@
         <v>400</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F42" t="n">
-        <v>627</v>
+        <v>333</v>
       </c>
       <c r="G42" t="n">
-        <v>627</v>
+        <v>137</v>
       </c>
       <c r="H42" t="n">
-        <v>627</v>
+        <v>137</v>
       </c>
       <c r="I42" t="n">
-        <v>627</v>
+        <v>537</v>
       </c>
       <c r="J42" t="n">
-        <v>627</v>
+        <v>537</v>
       </c>
       <c r="K42" t="n">
-        <v>627</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43">
@@ -8370,25 +8730,25 @@
         <v>200</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F43" t="n">
-        <v>306</v>
+        <v>-312</v>
       </c>
       <c r="G43" t="n">
-        <v>306</v>
+        <v>-312</v>
       </c>
       <c r="H43" t="n">
-        <v>306</v>
+        <v>-112</v>
       </c>
       <c r="I43" t="n">
-        <v>306</v>
+        <v>-112</v>
       </c>
       <c r="J43" t="n">
-        <v>306</v>
+        <v>-112</v>
       </c>
       <c r="K43" t="n">
-        <v>506</v>
+        <v>-112</v>
       </c>
     </row>
     <row r="44">
@@ -8409,25 +8769,25 @@
         <v>500</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="F44" t="n">
-        <v>723</v>
+        <v>37</v>
       </c>
       <c r="G44" t="n">
-        <v>723</v>
+        <v>-247</v>
       </c>
       <c r="H44" t="n">
-        <v>723</v>
+        <v>253</v>
       </c>
       <c r="I44" t="n">
-        <v>723</v>
+        <v>253</v>
       </c>
       <c r="J44" t="n">
-        <v>723</v>
+        <v>253</v>
       </c>
       <c r="K44" t="n">
-        <v>1223</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45">
@@ -8448,25 +8808,25 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F45" t="n">
-        <v>633</v>
+        <v>241</v>
       </c>
       <c r="G45" t="n">
-        <v>633</v>
+        <v>45</v>
       </c>
       <c r="H45" t="n">
-        <v>633</v>
+        <v>45</v>
       </c>
       <c r="I45" t="n">
-        <v>633</v>
+        <v>45</v>
       </c>
       <c r="J45" t="n">
-        <v>633</v>
+        <v>45</v>
       </c>
       <c r="K45" t="n">
-        <v>633</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -8487,25 +8847,25 @@
         <v>800</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="F46" t="n">
-        <v>94</v>
+        <v>-102</v>
       </c>
       <c r="G46" t="n">
-        <v>94</v>
+        <v>-200</v>
       </c>
       <c r="H46" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>94</v>
+        <v>-94</v>
       </c>
       <c r="J46" t="n">
-        <v>94</v>
+        <v>-90</v>
       </c>
       <c r="K46" t="n">
-        <v>294</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="47">
@@ -8526,25 +8886,25 @@
         <v>500</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F47" t="n">
-        <v>607</v>
+        <v>411</v>
       </c>
       <c r="G47" t="n">
-        <v>607</v>
+        <v>215</v>
       </c>
       <c r="H47" t="n">
-        <v>607</v>
+        <v>715</v>
       </c>
       <c r="I47" t="n">
-        <v>607</v>
+        <v>715</v>
       </c>
       <c r="J47" t="n">
-        <v>607</v>
+        <v>715</v>
       </c>
       <c r="K47" t="n">
-        <v>1107</v>
+        <v>715</v>
       </c>
     </row>
     <row r="48">
@@ -8565,25 +8925,25 @@
         <v>650</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F48" t="n">
-        <v>297</v>
+        <v>199</v>
       </c>
       <c r="G48" t="n">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="H48" t="n">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="I48" t="n">
-        <v>297</v>
+        <v>653</v>
       </c>
       <c r="J48" t="n">
-        <v>797</v>
+        <v>653</v>
       </c>
       <c r="K48" t="n">
-        <v>797</v>
+        <v>653</v>
       </c>
     </row>
     <row r="49">
@@ -8607,22 +8967,22 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="G49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="H49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="I49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="J49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="K49" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="50">
@@ -8643,25 +9003,25 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F50" t="n">
-        <v>743</v>
+        <v>547</v>
       </c>
       <c r="G50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="H50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="I50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="J50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="K50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
     </row>
     <row r="51">
@@ -8685,22 +9045,22 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="52">
@@ -8721,25 +9081,25 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="G52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="H52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="I52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="J52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="K52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
     </row>
     <row r="53">
@@ -8760,25 +9120,25 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F53" t="n">
-        <v>394</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>394</v>
+        <v>-194</v>
       </c>
       <c r="H53" t="n">
-        <v>394</v>
+        <v>-194</v>
       </c>
       <c r="I53" t="n">
-        <v>394</v>
+        <v>-194</v>
       </c>
       <c r="J53" t="n">
-        <v>394</v>
+        <v>-194</v>
       </c>
       <c r="K53" t="n">
-        <v>394</v>
+        <v>-194</v>
       </c>
     </row>
     <row r="54">
@@ -8799,25 +9159,25 @@
         <v>592</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F54" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="G54" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="H54" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="I54" t="n">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="J54" t="n">
-        <v>428</v>
+        <v>334</v>
       </c>
       <c r="K54" t="n">
-        <v>428</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55">
@@ -8838,25 +9198,25 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="G55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="H55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="I55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="J55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
@@ -8877,25 +9237,25 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F56" t="n">
-        <v>489</v>
+        <v>145</v>
       </c>
       <c r="G56" t="n">
-        <v>489</v>
+        <v>47</v>
       </c>
       <c r="H56" t="n">
-        <v>489</v>
+        <v>47</v>
       </c>
       <c r="I56" t="n">
-        <v>489</v>
+        <v>47</v>
       </c>
       <c r="J56" t="n">
-        <v>489</v>
+        <v>47</v>
       </c>
       <c r="K56" t="n">
-        <v>489</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57">
@@ -8916,25 +9276,25 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="F57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="G57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="H57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="I57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="J57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="K57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
     </row>
     <row r="58">
@@ -8955,25 +9315,25 @@
         <v>200</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -8994,25 +9354,25 @@
         <v>400</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F59" t="n">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="G59" t="n">
-        <v>246</v>
+        <v>346</v>
       </c>
       <c r="H59" t="n">
-        <v>246</v>
+        <v>346</v>
       </c>
       <c r="I59" t="n">
-        <v>246</v>
+        <v>346</v>
       </c>
       <c r="J59" t="n">
-        <v>646</v>
+        <v>346</v>
       </c>
       <c r="K59" t="n">
-        <v>646</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60">
@@ -9033,10 +9393,10 @@
         <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>495</v>
+        <v>295</v>
       </c>
       <c r="G60" t="n">
         <v>495</v>
@@ -9048,10 +9408,10 @@
         <v>495</v>
       </c>
       <c r="J60" t="n">
-        <v>695</v>
+        <v>495</v>
       </c>
       <c r="K60" t="n">
-        <v>695</v>
+        <v>495</v>
       </c>
     </row>
     <row r="61">
@@ -9072,25 +9432,25 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c r="G61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="H61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="I61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="J61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="K61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
@@ -9111,25 +9471,25 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F62" t="n">
-        <v>705</v>
+        <v>405</v>
       </c>
       <c r="G62" t="n">
-        <v>705</v>
+        <v>305</v>
       </c>
       <c r="H62" t="n">
-        <v>705</v>
+        <v>305</v>
       </c>
       <c r="I62" t="n">
-        <v>705</v>
+        <v>305</v>
       </c>
       <c r="J62" t="n">
-        <v>705</v>
+        <v>305</v>
       </c>
       <c r="K62" t="n">
-        <v>705</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63">
@@ -9150,25 +9510,25 @@
         <v>339</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="G63" t="n">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="H63" t="n">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="I63" t="n">
-        <v>517</v>
+        <v>367</v>
       </c>
       <c r="J63" t="n">
-        <v>517</v>
+        <v>367</v>
       </c>
       <c r="K63" t="n">
-        <v>517</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -11396,16 +11756,16 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="H13" t="n">
-        <v>261</v>
+        <v>381</v>
       </c>
       <c r="I13" t="n">
-        <v>381</v>
+        <v>741</v>
       </c>
       <c r="J13" t="n">
-        <v>741</v>
+        <v>1161</v>
       </c>
       <c r="K13" t="n">
         <v>1161</v>
@@ -11438,13 +11798,13 @@
         <v>475</v>
       </c>
       <c r="H14" t="n">
-        <v>475</v>
+        <v>595</v>
       </c>
       <c r="I14" t="n">
-        <v>595</v>
+        <v>1015</v>
       </c>
       <c r="J14" t="n">
-        <v>1015</v>
+        <v>1375</v>
       </c>
       <c r="K14" t="n">
         <v>1375</v>
@@ -11471,13 +11831,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="G15" t="n">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="H15" t="n">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="I15" t="n">
         <v>441</v>
@@ -11513,16 +11873,16 @@
         <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>72</v>
+        <v>312</v>
       </c>
       <c r="H16" t="n">
-        <v>312</v>
+        <v>432</v>
       </c>
       <c r="I16" t="n">
-        <v>432</v>
+        <v>672</v>
       </c>
       <c r="J16" t="n">
-        <v>672</v>
+        <v>912</v>
       </c>
       <c r="K16" t="n">
         <v>912</v>
@@ -11549,13 +11909,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="G17" t="n">
         <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>307</v>
+        <v>487</v>
       </c>
       <c r="I17" t="n">
         <v>487</v>
@@ -11588,13 +11948,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>132</v>
+        <v>431</v>
       </c>
       <c r="G18" t="n">
-        <v>431</v>
+        <v>1017</v>
       </c>
       <c r="H18" t="n">
-        <v>1017</v>
+        <v>1257</v>
       </c>
       <c r="I18" t="n">
         <v>1257</v>
@@ -11633,7 +11993,7 @@
         <v>106</v>
       </c>
       <c r="H19" t="n">
-        <v>106</v>
+        <v>286</v>
       </c>
       <c r="I19" t="n">
         <v>286</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -11750,25 +11750,25 @@
         <v>1080</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>-59</v>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
+        <v>-19</v>
       </c>
       <c r="H13" t="n">
-        <v>381</v>
+        <v>-74</v>
       </c>
       <c r="I13" t="n">
-        <v>741</v>
+        <v>-64</v>
       </c>
       <c r="J13" t="n">
-        <v>1161</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>1161</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14">
@@ -11789,25 +11789,25 @@
         <v>900</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="F14" t="n">
-        <v>475</v>
+        <v>370</v>
       </c>
       <c r="G14" t="n">
-        <v>475</v>
+        <v>265</v>
       </c>
       <c r="H14" t="n">
-        <v>595</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
-        <v>1015</v>
+        <v>105</v>
       </c>
       <c r="J14" t="n">
-        <v>1375</v>
+        <v>465</v>
       </c>
       <c r="K14" t="n">
-        <v>1375</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15">
@@ -11867,25 +11867,25 @@
         <v>840</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>-33</v>
       </c>
       <c r="G16" t="n">
-        <v>312</v>
+        <v>102</v>
       </c>
       <c r="H16" t="n">
-        <v>432</v>
+        <v>47</v>
       </c>
       <c r="I16" t="n">
-        <v>672</v>
+        <v>77</v>
       </c>
       <c r="J16" t="n">
-        <v>912</v>
+        <v>317</v>
       </c>
       <c r="K16" t="n">
-        <v>912</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17">
@@ -11906,7 +11906,7 @@
         <v>354</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="F17" t="n">
         <v>307</v>
@@ -11915,16 +11915,16 @@
         <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>487</v>
+        <v>312</v>
       </c>
       <c r="I17" t="n">
-        <v>487</v>
+        <v>312</v>
       </c>
       <c r="J17" t="n">
-        <v>487</v>
+        <v>312</v>
       </c>
       <c r="K17" t="n">
-        <v>487</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18">
@@ -11945,25 +11945,25 @@
         <v>1125</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="F18" t="n">
-        <v>431</v>
+        <v>-164</v>
       </c>
       <c r="G18" t="n">
-        <v>1017</v>
+        <v>-138</v>
       </c>
       <c r="H18" t="n">
-        <v>1257</v>
+        <v>102</v>
       </c>
       <c r="I18" t="n">
-        <v>1257</v>
+        <v>102</v>
       </c>
       <c r="J18" t="n">
-        <v>1257</v>
+        <v>102</v>
       </c>
       <c r="K18" t="n">
-        <v>1257</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
@@ -11984,7 +11984,7 @@
         <v>180</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
         <v>106</v>
@@ -11993,16 +11993,16 @@
         <v>106</v>
       </c>
       <c r="H19" t="n">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="I19" t="n">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="J19" t="n">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>286</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S23</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -691,20 +691,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE21029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>2,75-3,50 x 19</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>312</v>
+        <v>476</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -751,20 +751,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE21032</t>
+          <t>SE21031</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 24</t>
+          <t>2,00-2,5 x 24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -781,20 +781,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE21032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2,75-3,5 x 24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S26</t>
         </is>
       </c>
     </row>
@@ -901,16 +901,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE21034</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2,00-2,5 x 29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE21041</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2,75-3,5 x 39</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -961,20 +961,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SE21034</t>
+          <t>SE21041</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 29</t>
+          <t>2,75-3,5 x 39</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S26</t>
         </is>
       </c>
     </row>
@@ -991,16 +991,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SE21041</t>
+          <t>SE21028</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 39</t>
+          <t>2,00-2,5 x 19</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1021,16 +1021,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SE21041</t>
+          <t>SE21028</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 39</t>
+          <t>2,00-2,5 x 19</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SE21041</t>
+          <t>SE21028</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 39</t>
+          <t>2,00-2,5 x 19</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -8379,19 +8379,19 @@
         <v>199</v>
       </c>
       <c r="E34" t="n">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="F34" t="n">
+        <v>135</v>
+      </c>
+      <c r="G34" t="n">
+        <v>135</v>
+      </c>
+      <c r="H34" t="n">
         <v>37</v>
       </c>
-      <c r="G34" t="n">
-        <v>40</v>
-      </c>
-      <c r="H34" t="n">
-        <v>40</v>
-      </c>
       <c r="I34" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J34" t="n">
         <v>40</v>
@@ -8418,25 +8418,25 @@
         <v>399</v>
       </c>
       <c r="E35" t="n">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="F35" t="n">
+        <v>52</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-46</v>
+      </c>
+      <c r="H35" t="n">
         <v>-94</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
+        <v>-94</v>
+      </c>
+      <c r="J35" t="n">
         <v>-91</v>
       </c>
-      <c r="H35" t="n">
+      <c r="K35" t="n">
         <v>-91</v>
-      </c>
-      <c r="I35" t="n">
-        <v>109</v>
-      </c>
-      <c r="J35" t="n">
-        <v>109</v>
-      </c>
-      <c r="K35" t="n">
-        <v>109</v>
       </c>
     </row>
     <row r="36">
@@ -8457,25 +8457,25 @@
         <v>549</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F36" t="n">
+        <v>176</v>
+      </c>
+      <c r="G36" t="n">
+        <v>176</v>
+      </c>
+      <c r="H36" t="n">
         <v>78</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
+        <v>78</v>
+      </c>
+      <c r="J36" t="n">
         <v>277</v>
       </c>
-      <c r="H36" t="n">
+      <c r="K36" t="n">
         <v>277</v>
-      </c>
-      <c r="I36" t="n">
-        <v>627</v>
-      </c>
-      <c r="J36" t="n">
-        <v>627</v>
-      </c>
-      <c r="K36" t="n">
-        <v>627</v>
       </c>
     </row>
     <row r="37">
@@ -8496,25 +8496,25 @@
         <v>800</v>
       </c>
       <c r="E37" t="n">
-        <v>784</v>
+        <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>-44</v>
       </c>
       <c r="H37" t="n">
+        <v>-44</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-44</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-44</v>
+      </c>
+      <c r="K37" t="n">
         <v>156</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-36</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-32</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-28</v>
       </c>
     </row>
     <row r="38">
@@ -8535,25 +8535,25 @@
         <v>550</v>
       </c>
       <c r="E38" t="n">
-        <v>294</v>
+        <v>588</v>
       </c>
       <c r="F38" t="n">
+        <v>546</v>
+      </c>
+      <c r="G38" t="n">
+        <v>546</v>
+      </c>
+      <c r="H38" t="n">
+        <v>252</v>
+      </c>
+      <c r="I38" t="n">
         <v>-42</v>
       </c>
-      <c r="G38" t="n">
+      <c r="J38" t="n">
         <v>108</v>
       </c>
-      <c r="H38" t="n">
+      <c r="K38" t="n">
         <v>108</v>
-      </c>
-      <c r="I38" t="n">
-        <v>508</v>
-      </c>
-      <c r="J38" t="n">
-        <v>508</v>
-      </c>
-      <c r="K38" t="n">
-        <v>508</v>
       </c>
     </row>
     <row r="39">
@@ -8574,25 +8574,25 @@
         <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>294</v>
+        <v>490</v>
       </c>
       <c r="F39" t="n">
+        <v>545</v>
+      </c>
+      <c r="G39" t="n">
+        <v>349</v>
+      </c>
+      <c r="H39" t="n">
+        <v>349</v>
+      </c>
+      <c r="I39" t="n">
         <v>153</v>
       </c>
-      <c r="G39" t="n">
+      <c r="J39" t="n">
         <v>55</v>
       </c>
-      <c r="H39" t="n">
+      <c r="K39" t="n">
         <v>55</v>
-      </c>
-      <c r="I39" t="n">
-        <v>255</v>
-      </c>
-      <c r="J39" t="n">
-        <v>255</v>
-      </c>
-      <c r="K39" t="n">
-        <v>255</v>
       </c>
     </row>
     <row r="40">
@@ -8613,25 +8613,25 @@
         <v>800</v>
       </c>
       <c r="E40" t="n">
-        <v>784</v>
+        <v>196</v>
       </c>
       <c r="F40" t="n">
-        <v>-190</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>-190</v>
       </c>
       <c r="H40" t="n">
+        <v>-190</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-190</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-190</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-182</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-178</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-174</v>
       </c>
     </row>
     <row r="41">
@@ -8652,22 +8652,22 @@
         <v>700</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="F41" t="n">
+        <v>210</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84</v>
+      </c>
+      <c r="H41" t="n">
         <v>-476</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>-476</v>
       </c>
-      <c r="H41" t="n">
-        <v>224</v>
-      </c>
-      <c r="I41" t="n">
-        <v>224</v>
-      </c>
       <c r="J41" t="n">
-        <v>224</v>
+        <v>-476</v>
       </c>
       <c r="K41" t="n">
         <v>224</v>
@@ -8691,25 +8691,25 @@
         <v>400</v>
       </c>
       <c r="E42" t="n">
-        <v>294</v>
+        <v>490</v>
       </c>
       <c r="F42" t="n">
+        <v>529</v>
+      </c>
+      <c r="G42" t="n">
+        <v>529</v>
+      </c>
+      <c r="H42" t="n">
+        <v>431</v>
+      </c>
+      <c r="I42" t="n">
         <v>333</v>
       </c>
-      <c r="G42" t="n">
+      <c r="J42" t="n">
         <v>137</v>
       </c>
-      <c r="H42" t="n">
+      <c r="K42" t="n">
         <v>137</v>
-      </c>
-      <c r="I42" t="n">
-        <v>537</v>
-      </c>
-      <c r="J42" t="n">
-        <v>537</v>
-      </c>
-      <c r="K42" t="n">
-        <v>537</v>
       </c>
     </row>
     <row r="43">
@@ -8730,22 +8730,22 @@
         <v>200</v>
       </c>
       <c r="E43" t="n">
-        <v>196</v>
+        <v>618</v>
       </c>
       <c r="F43" t="n">
+        <v>208</v>
+      </c>
+      <c r="G43" t="n">
+        <v>110</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I43" t="n">
         <v>-312</v>
       </c>
-      <c r="G43" t="n">
+      <c r="J43" t="n">
         <v>-312</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-112</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-112</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-112</v>
       </c>
       <c r="K43" t="n">
         <v>-112</v>
@@ -8769,22 +8769,22 @@
         <v>500</v>
       </c>
       <c r="E44" t="n">
-        <v>382</v>
+        <v>970</v>
       </c>
       <c r="F44" t="n">
+        <v>527</v>
+      </c>
+      <c r="G44" t="n">
+        <v>331</v>
+      </c>
+      <c r="H44" t="n">
+        <v>135</v>
+      </c>
+      <c r="I44" t="n">
         <v>37</v>
       </c>
-      <c r="G44" t="n">
+      <c r="J44" t="n">
         <v>-247</v>
-      </c>
-      <c r="H44" t="n">
-        <v>253</v>
-      </c>
-      <c r="I44" t="n">
-        <v>253</v>
-      </c>
-      <c r="J44" t="n">
-        <v>253</v>
       </c>
       <c r="K44" t="n">
         <v>253</v>
@@ -8808,19 +8808,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>196</v>
+        <v>588</v>
       </c>
       <c r="F45" t="n">
+        <v>535</v>
+      </c>
+      <c r="G45" t="n">
+        <v>535</v>
+      </c>
+      <c r="H45" t="n">
         <v>241</v>
       </c>
-      <c r="G45" t="n">
-        <v>45</v>
-      </c>
-      <c r="H45" t="n">
-        <v>45</v>
-      </c>
       <c r="I45" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="J45" t="n">
         <v>45</v>
@@ -8847,25 +8847,25 @@
         <v>800</v>
       </c>
       <c r="E46" t="n">
-        <v>882</v>
+        <v>294</v>
       </c>
       <c r="F46" t="n">
+        <v>94</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I46" t="n">
         <v>-102</v>
       </c>
-      <c r="G46" t="n">
+      <c r="J46" t="n">
         <v>-200</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-94</v>
-      </c>
-      <c r="J46" t="n">
-        <v>-90</v>
-      </c>
       <c r="K46" t="n">
-        <v>-86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -8886,22 +8886,22 @@
         <v>500</v>
       </c>
       <c r="E47" t="n">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="F47" t="n">
         <v>411</v>
       </c>
       <c r="G47" t="n">
+        <v>411</v>
+      </c>
+      <c r="H47" t="n">
+        <v>411</v>
+      </c>
+      <c r="I47" t="n">
+        <v>411</v>
+      </c>
+      <c r="J47" t="n">
         <v>215</v>
-      </c>
-      <c r="H47" t="n">
-        <v>715</v>
-      </c>
-      <c r="I47" t="n">
-        <v>715</v>
-      </c>
-      <c r="J47" t="n">
-        <v>715</v>
       </c>
       <c r="K47" t="n">
         <v>715</v>
@@ -8925,25 +8925,25 @@
         <v>650</v>
       </c>
       <c r="E48" t="n">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="F48" t="n">
+        <v>297</v>
+      </c>
+      <c r="G48" t="n">
         <v>199</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
+        <v>199</v>
+      </c>
+      <c r="I48" t="n">
+        <v>199</v>
+      </c>
+      <c r="J48" t="n">
         <v>503</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>503</v>
-      </c>
-      <c r="I48" t="n">
-        <v>653</v>
-      </c>
-      <c r="J48" t="n">
-        <v>653</v>
-      </c>
-      <c r="K48" t="n">
-        <v>653</v>
       </c>
     </row>
     <row r="49">
@@ -8964,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F49" t="n">
         <v>-46</v>
@@ -9006,16 +9006,16 @@
         <v>294</v>
       </c>
       <c r="F50" t="n">
+        <v>743</v>
+      </c>
+      <c r="G50" t="n">
+        <v>743</v>
+      </c>
+      <c r="H50" t="n">
+        <v>743</v>
+      </c>
+      <c r="I50" t="n">
         <v>547</v>
-      </c>
-      <c r="G50" t="n">
-        <v>449</v>
-      </c>
-      <c r="H50" t="n">
-        <v>449</v>
-      </c>
-      <c r="I50" t="n">
-        <v>449</v>
       </c>
       <c r="J50" t="n">
         <v>449</v>
@@ -9042,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F51" t="n">
         <v>-95</v>
@@ -9081,16 +9081,16 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>382</v>
       </c>
       <c r="F52" t="n">
-        <v>-243</v>
+        <v>139</v>
       </c>
       <c r="G52" t="n">
-        <v>-243</v>
+        <v>-145</v>
       </c>
       <c r="H52" t="n">
-        <v>-243</v>
+        <v>-145</v>
       </c>
       <c r="I52" t="n">
         <v>-243</v>
@@ -9120,19 +9120,19 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>294</v>
+        <v>588</v>
       </c>
       <c r="F53" t="n">
+        <v>296</v>
+      </c>
+      <c r="G53" t="n">
         <v>100</v>
       </c>
-      <c r="G53" t="n">
-        <v>-194</v>
-      </c>
       <c r="H53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
         <v>-194</v>
@@ -9159,25 +9159,25 @@
         <v>592</v>
       </c>
       <c r="E54" t="n">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="F54" t="n">
+        <v>36</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-62</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I54" t="n">
         <v>134</v>
       </c>
-      <c r="G54" t="n">
+      <c r="J54" t="n">
         <v>134</v>
       </c>
-      <c r="H54" t="n">
+      <c r="K54" t="n">
         <v>134</v>
-      </c>
-      <c r="I54" t="n">
-        <v>334</v>
-      </c>
-      <c r="J54" t="n">
-        <v>334</v>
-      </c>
-      <c r="K54" t="n">
-        <v>334</v>
       </c>
     </row>
     <row r="55">
@@ -9198,16 +9198,16 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="F55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="G55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="H55" t="n">
-        <v>41</v>
+        <v>237</v>
       </c>
       <c r="I55" t="n">
         <v>41</v>
@@ -9237,19 +9237,19 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>186</v>
+        <v>442</v>
       </c>
       <c r="F56" t="n">
+        <v>391</v>
+      </c>
+      <c r="G56" t="n">
+        <v>391</v>
+      </c>
+      <c r="H56" t="n">
+        <v>233</v>
+      </c>
+      <c r="I56" t="n">
         <v>145</v>
-      </c>
-      <c r="G56" t="n">
-        <v>47</v>
-      </c>
-      <c r="H56" t="n">
-        <v>47</v>
-      </c>
-      <c r="I56" t="n">
-        <v>47</v>
       </c>
       <c r="J56" t="n">
         <v>47</v>
@@ -9279,13 +9279,13 @@
         <v>196</v>
       </c>
       <c r="F57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="G57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="H57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="I57" t="n">
         <v>461</v>
@@ -9315,19 +9315,19 @@
         <v>200</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>-50</v>
       </c>
-      <c r="G58" t="n">
-        <v>50</v>
-      </c>
       <c r="H58" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="J58" t="n">
         <v>50</v>
@@ -9354,19 +9354,19 @@
         <v>400</v>
       </c>
       <c r="E59" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F59" t="n">
+        <v>246</v>
+      </c>
+      <c r="G59" t="n">
+        <v>146</v>
+      </c>
+      <c r="H59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I59" t="n">
         <v>46</v>
-      </c>
-      <c r="G59" t="n">
-        <v>346</v>
-      </c>
-      <c r="H59" t="n">
-        <v>346</v>
-      </c>
-      <c r="I59" t="n">
-        <v>346</v>
       </c>
       <c r="J59" t="n">
         <v>346</v>
@@ -9393,19 +9393,19 @@
         <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F60" t="n">
+        <v>495</v>
+      </c>
+      <c r="G60" t="n">
+        <v>395</v>
+      </c>
+      <c r="H60" t="n">
+        <v>345</v>
+      </c>
+      <c r="I60" t="n">
         <v>295</v>
-      </c>
-      <c r="G60" t="n">
-        <v>495</v>
-      </c>
-      <c r="H60" t="n">
-        <v>495</v>
-      </c>
-      <c r="I60" t="n">
-        <v>495</v>
       </c>
       <c r="J60" t="n">
         <v>495</v>
@@ -9432,19 +9432,19 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F61" t="n">
+        <v>278</v>
+      </c>
+      <c r="G61" t="n">
+        <v>278</v>
+      </c>
+      <c r="H61" t="n">
+        <v>178</v>
+      </c>
+      <c r="I61" t="n">
         <v>128</v>
-      </c>
-      <c r="G61" t="n">
-        <v>78</v>
-      </c>
-      <c r="H61" t="n">
-        <v>78</v>
-      </c>
-      <c r="I61" t="n">
-        <v>78</v>
       </c>
       <c r="J61" t="n">
         <v>78</v>
@@ -9471,19 +9471,19 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F62" t="n">
+        <v>655</v>
+      </c>
+      <c r="G62" t="n">
+        <v>555</v>
+      </c>
+      <c r="H62" t="n">
+        <v>505</v>
+      </c>
+      <c r="I62" t="n">
         <v>405</v>
-      </c>
-      <c r="G62" t="n">
-        <v>305</v>
-      </c>
-      <c r="H62" t="n">
-        <v>305</v>
-      </c>
-      <c r="I62" t="n">
-        <v>305</v>
       </c>
       <c r="J62" t="n">
         <v>305</v>
@@ -9510,16 +9510,16 @@
         <v>339</v>
       </c>
       <c r="E63" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F63" t="n">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="G63" t="n">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="H63" t="n">
-        <v>367</v>
+        <v>128</v>
       </c>
       <c r="I63" t="n">
         <v>367</v>
@@ -11753,19 +11753,19 @@
         <v>805</v>
       </c>
       <c r="F13" t="n">
+        <v>81</v>
+      </c>
+      <c r="G13" t="n">
         <v>-59</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-19</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-74</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>356</v>
       </c>
       <c r="K13" t="n">
         <v>356</v>
@@ -11792,19 +11792,19 @@
         <v>910</v>
       </c>
       <c r="F14" t="n">
+        <v>475</v>
+      </c>
+      <c r="G14" t="n">
         <v>370</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>265</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>35</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>105</v>
-      </c>
-      <c r="J14" t="n">
-        <v>465</v>
       </c>
       <c r="K14" t="n">
         <v>465</v>
@@ -11831,13 +11831,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>265</v>
+      </c>
+      <c r="G15" t="n">
         <v>325</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>381</v>
-      </c>
-      <c r="H15" t="n">
-        <v>441</v>
       </c>
       <c r="I15" t="n">
         <v>441</v>
@@ -11870,19 +11870,19 @@
         <v>595</v>
       </c>
       <c r="F16" t="n">
+        <v>72</v>
+      </c>
+      <c r="G16" t="n">
         <v>-33</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>102</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>47</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>77</v>
-      </c>
-      <c r="J16" t="n">
-        <v>317</v>
       </c>
       <c r="K16" t="n">
         <v>317</v>
@@ -11909,13 +11909,13 @@
         <v>175</v>
       </c>
       <c r="F17" t="n">
-        <v>307</v>
+        <v>133</v>
       </c>
       <c r="G17" t="n">
         <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I17" t="n">
         <v>312</v>
@@ -11945,16 +11945,16 @@
         <v>1125</v>
       </c>
       <c r="E18" t="n">
-        <v>1085</v>
+        <v>1155</v>
       </c>
       <c r="F18" t="n">
+        <v>62</v>
+      </c>
+      <c r="G18" t="n">
         <v>-164</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-138</v>
-      </c>
-      <c r="H18" t="n">
-        <v>102</v>
       </c>
       <c r="I18" t="n">
         <v>102</v>
@@ -11993,7 +11993,7 @@
         <v>106</v>
       </c>
       <c r="H19" t="n">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="I19" t="n">
         <v>251</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -691,20 +691,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SE21029</t>
+          <t>SE21031</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 19</t>
+          <t>2,00-2,5 x 24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>476</v>
+        <v>312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -751,20 +751,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE21032</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>2,75-3,5 x 24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -781,20 +781,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE21032</t>
+          <t>SE21040</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 24</t>
+          <t>2,00-2,5 x 39</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S23</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -901,16 +901,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SE21034</t>
+          <t>SE21040</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 29</t>
+          <t>2,00-2,5 x 39</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SE21041</t>
+          <t>SE21040</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 39</t>
+          <t>2,00-2,5 x 39</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S26</t>
         </is>
       </c>
     </row>
@@ -961,20 +961,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SE21041</t>
+          <t>SE21034</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 39</t>
+          <t>2,00-2,5 x 29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -991,16 +991,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SE21028</t>
+          <t>SE21041</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 19</t>
+          <t>2,75-3,5 x 39</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1021,16 +1021,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SE21028</t>
+          <t>SE21041</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 19</t>
+          <t>2,75-3,5 x 39</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SE21028</t>
+          <t>SE21041</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 19</t>
+          <t>2,75-3,5 x 39</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
@@ -8382,16 +8382,16 @@
         <v>294</v>
       </c>
       <c r="F34" t="n">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="H34" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I34" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J34" t="n">
         <v>40</v>
@@ -8421,22 +8421,22 @@
         <v>342</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>-94</v>
       </c>
       <c r="G35" t="n">
-        <v>-46</v>
+        <v>-91</v>
       </c>
       <c r="H35" t="n">
-        <v>-94</v>
+        <v>-91</v>
       </c>
       <c r="I35" t="n">
-        <v>-94</v>
+        <v>109</v>
       </c>
       <c r="J35" t="n">
-        <v>-91</v>
+        <v>109</v>
       </c>
       <c r="K35" t="n">
-        <v>-91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36">
@@ -8460,22 +8460,22 @@
         <v>98</v>
       </c>
       <c r="F36" t="n">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="G36" t="n">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="H36" t="n">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="I36" t="n">
-        <v>78</v>
+        <v>627</v>
       </c>
       <c r="J36" t="n">
-        <v>277</v>
+        <v>627</v>
       </c>
       <c r="K36" t="n">
-        <v>277</v>
+        <v>627</v>
       </c>
     </row>
     <row r="37">
@@ -8499,22 +8499,22 @@
         <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>-44</v>
       </c>
       <c r="G37" t="n">
         <v>-44</v>
       </c>
       <c r="H37" t="n">
-        <v>-44</v>
+        <v>156</v>
       </c>
       <c r="I37" t="n">
-        <v>-44</v>
+        <v>-36</v>
       </c>
       <c r="J37" t="n">
-        <v>-44</v>
+        <v>-32</v>
       </c>
       <c r="K37" t="n">
-        <v>156</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="38">
@@ -8538,22 +8538,22 @@
         <v>588</v>
       </c>
       <c r="F38" t="n">
-        <v>546</v>
+        <v>-42</v>
       </c>
       <c r="G38" t="n">
-        <v>546</v>
+        <v>108</v>
       </c>
       <c r="H38" t="n">
-        <v>252</v>
+        <v>108</v>
       </c>
       <c r="I38" t="n">
-        <v>-42</v>
+        <v>508</v>
       </c>
       <c r="J38" t="n">
-        <v>108</v>
+        <v>508</v>
       </c>
       <c r="K38" t="n">
-        <v>108</v>
+        <v>508</v>
       </c>
     </row>
     <row r="39">
@@ -8577,22 +8577,22 @@
         <v>490</v>
       </c>
       <c r="F39" t="n">
-        <v>545</v>
+        <v>153</v>
       </c>
       <c r="G39" t="n">
-        <v>349</v>
+        <v>55</v>
       </c>
       <c r="H39" t="n">
-        <v>349</v>
+        <v>55</v>
       </c>
       <c r="I39" t="n">
-        <v>153</v>
+        <v>255</v>
       </c>
       <c r="J39" t="n">
-        <v>55</v>
+        <v>255</v>
       </c>
       <c r="K39" t="n">
-        <v>55</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40">
@@ -8616,22 +8616,22 @@
         <v>196</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>-190</v>
       </c>
       <c r="G40" t="n">
         <v>-190</v>
       </c>
       <c r="H40" t="n">
-        <v>-190</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>-190</v>
+        <v>-182</v>
       </c>
       <c r="J40" t="n">
-        <v>-190</v>
+        <v>-178</v>
       </c>
       <c r="K40" t="n">
-        <v>10</v>
+        <v>-174</v>
       </c>
     </row>
     <row r="41">
@@ -8655,19 +8655,19 @@
         <v>882</v>
       </c>
       <c r="F41" t="n">
-        <v>210</v>
+        <v>-476</v>
       </c>
       <c r="G41" t="n">
-        <v>-84</v>
+        <v>-476</v>
       </c>
       <c r="H41" t="n">
-        <v>-476</v>
+        <v>224</v>
       </c>
       <c r="I41" t="n">
-        <v>-476</v>
+        <v>224</v>
       </c>
       <c r="J41" t="n">
-        <v>-476</v>
+        <v>224</v>
       </c>
       <c r="K41" t="n">
         <v>224</v>
@@ -8694,22 +8694,22 @@
         <v>490</v>
       </c>
       <c r="F42" t="n">
-        <v>529</v>
+        <v>333</v>
       </c>
       <c r="G42" t="n">
-        <v>529</v>
+        <v>137</v>
       </c>
       <c r="H42" t="n">
-        <v>431</v>
+        <v>137</v>
       </c>
       <c r="I42" t="n">
-        <v>333</v>
+        <v>537</v>
       </c>
       <c r="J42" t="n">
-        <v>137</v>
+        <v>537</v>
       </c>
       <c r="K42" t="n">
-        <v>137</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43">
@@ -8733,19 +8733,19 @@
         <v>618</v>
       </c>
       <c r="F43" t="n">
-        <v>208</v>
+        <v>-312</v>
       </c>
       <c r="G43" t="n">
-        <v>110</v>
+        <v>-312</v>
       </c>
       <c r="H43" t="n">
-        <v>-116</v>
+        <v>-112</v>
       </c>
       <c r="I43" t="n">
-        <v>-312</v>
+        <v>-112</v>
       </c>
       <c r="J43" t="n">
-        <v>-312</v>
+        <v>-112</v>
       </c>
       <c r="K43" t="n">
         <v>-112</v>
@@ -8772,19 +8772,19 @@
         <v>970</v>
       </c>
       <c r="F44" t="n">
-        <v>527</v>
+        <v>37</v>
       </c>
       <c r="G44" t="n">
-        <v>331</v>
+        <v>-247</v>
       </c>
       <c r="H44" t="n">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="I44" t="n">
-        <v>37</v>
+        <v>253</v>
       </c>
       <c r="J44" t="n">
-        <v>-247</v>
+        <v>253</v>
       </c>
       <c r="K44" t="n">
         <v>253</v>
@@ -8811,16 +8811,16 @@
         <v>588</v>
       </c>
       <c r="F45" t="n">
-        <v>535</v>
+        <v>241</v>
       </c>
       <c r="G45" t="n">
-        <v>535</v>
+        <v>45</v>
       </c>
       <c r="H45" t="n">
-        <v>241</v>
+        <v>45</v>
       </c>
       <c r="I45" t="n">
-        <v>241</v>
+        <v>45</v>
       </c>
       <c r="J45" t="n">
         <v>45</v>
@@ -8850,22 +8850,22 @@
         <v>294</v>
       </c>
       <c r="F46" t="n">
-        <v>94</v>
+        <v>-102</v>
       </c>
       <c r="G46" t="n">
-        <v>-4</v>
+        <v>-200</v>
       </c>
       <c r="H46" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>-102</v>
+        <v>-94</v>
       </c>
       <c r="J46" t="n">
-        <v>-200</v>
+        <v>-90</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="47">
@@ -8892,16 +8892,16 @@
         <v>411</v>
       </c>
       <c r="G47" t="n">
-        <v>411</v>
+        <v>215</v>
       </c>
       <c r="H47" t="n">
-        <v>411</v>
+        <v>715</v>
       </c>
       <c r="I47" t="n">
-        <v>411</v>
+        <v>715</v>
       </c>
       <c r="J47" t="n">
-        <v>215</v>
+        <v>715</v>
       </c>
       <c r="K47" t="n">
         <v>715</v>
@@ -8928,22 +8928,22 @@
         <v>294</v>
       </c>
       <c r="F48" t="n">
-        <v>297</v>
+        <v>199</v>
       </c>
       <c r="G48" t="n">
-        <v>199</v>
+        <v>503</v>
       </c>
       <c r="H48" t="n">
-        <v>199</v>
+        <v>503</v>
       </c>
       <c r="I48" t="n">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="J48" t="n">
-        <v>503</v>
+        <v>653</v>
       </c>
       <c r="K48" t="n">
-        <v>503</v>
+        <v>653</v>
       </c>
     </row>
     <row r="49">
@@ -9006,16 +9006,16 @@
         <v>294</v>
       </c>
       <c r="F50" t="n">
-        <v>743</v>
+        <v>547</v>
       </c>
       <c r="G50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="H50" t="n">
-        <v>743</v>
+        <v>449</v>
       </c>
       <c r="I50" t="n">
-        <v>547</v>
+        <v>449</v>
       </c>
       <c r="J50" t="n">
         <v>449</v>
@@ -9084,13 +9084,13 @@
         <v>382</v>
       </c>
       <c r="F52" t="n">
-        <v>139</v>
+        <v>-243</v>
       </c>
       <c r="G52" t="n">
-        <v>-145</v>
+        <v>-243</v>
       </c>
       <c r="H52" t="n">
-        <v>-145</v>
+        <v>-243</v>
       </c>
       <c r="I52" t="n">
         <v>-243</v>
@@ -9123,16 +9123,16 @@
         <v>588</v>
       </c>
       <c r="F53" t="n">
-        <v>296</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>-194</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>-194</v>
       </c>
       <c r="I53" t="n">
-        <v>100</v>
+        <v>-194</v>
       </c>
       <c r="J53" t="n">
         <v>-194</v>
@@ -9162,22 +9162,22 @@
         <v>294</v>
       </c>
       <c r="F54" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="G54" t="n">
-        <v>-62</v>
+        <v>134</v>
       </c>
       <c r="H54" t="n">
-        <v>-62</v>
+        <v>134</v>
       </c>
       <c r="I54" t="n">
-        <v>134</v>
+        <v>334</v>
       </c>
       <c r="J54" t="n">
-        <v>134</v>
+        <v>334</v>
       </c>
       <c r="K54" t="n">
-        <v>134</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55">
@@ -9201,13 +9201,13 @@
         <v>294</v>
       </c>
       <c r="F55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="G55" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="H55" t="n">
-        <v>237</v>
+        <v>41</v>
       </c>
       <c r="I55" t="n">
         <v>41</v>
@@ -9240,16 +9240,16 @@
         <v>442</v>
       </c>
       <c r="F56" t="n">
-        <v>391</v>
+        <v>145</v>
       </c>
       <c r="G56" t="n">
-        <v>391</v>
+        <v>47</v>
       </c>
       <c r="H56" t="n">
-        <v>233</v>
+        <v>47</v>
       </c>
       <c r="I56" t="n">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="J56" t="n">
         <v>47</v>
@@ -9279,13 +9279,13 @@
         <v>196</v>
       </c>
       <c r="F57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="G57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="H57" t="n">
-        <v>657</v>
+        <v>461</v>
       </c>
       <c r="I57" t="n">
         <v>461</v>
@@ -9318,16 +9318,16 @@
         <v>150</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="G58" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I58" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
         <v>50</v>
@@ -9357,16 +9357,16 @@
         <v>300</v>
       </c>
       <c r="F59" t="n">
-        <v>246</v>
+        <v>46</v>
       </c>
       <c r="G59" t="n">
-        <v>146</v>
+        <v>346</v>
       </c>
       <c r="H59" t="n">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="I59" t="n">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="J59" t="n">
         <v>346</v>
@@ -9396,16 +9396,16 @@
         <v>200</v>
       </c>
       <c r="F60" t="n">
+        <v>295</v>
+      </c>
+      <c r="G60" t="n">
         <v>495</v>
       </c>
-      <c r="G60" t="n">
-        <v>395</v>
-      </c>
       <c r="H60" t="n">
-        <v>345</v>
+        <v>495</v>
       </c>
       <c r="I60" t="n">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="J60" t="n">
         <v>495</v>
@@ -9435,16 +9435,16 @@
         <v>200</v>
       </c>
       <c r="F61" t="n">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c r="G61" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="H61" t="n">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="I61" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="J61" t="n">
         <v>78</v>
@@ -9474,16 +9474,16 @@
         <v>400</v>
       </c>
       <c r="F62" t="n">
-        <v>655</v>
+        <v>405</v>
       </c>
       <c r="G62" t="n">
-        <v>555</v>
+        <v>305</v>
       </c>
       <c r="H62" t="n">
-        <v>505</v>
+        <v>305</v>
       </c>
       <c r="I62" t="n">
-        <v>405</v>
+        <v>305</v>
       </c>
       <c r="J62" t="n">
         <v>305</v>
@@ -9513,13 +9513,13 @@
         <v>150</v>
       </c>
       <c r="F63" t="n">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="G63" t="n">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="H63" t="n">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="I63" t="n">
         <v>367</v>
@@ -11753,19 +11753,19 @@
         <v>805</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>-59</v>
       </c>
       <c r="G13" t="n">
-        <v>-59</v>
+        <v>-19</v>
       </c>
       <c r="H13" t="n">
-        <v>-19</v>
+        <v>-74</v>
       </c>
       <c r="I13" t="n">
-        <v>-74</v>
+        <v>-64</v>
       </c>
       <c r="J13" t="n">
-        <v>-64</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
         <v>356</v>
@@ -11792,19 +11792,19 @@
         <v>910</v>
       </c>
       <c r="F14" t="n">
-        <v>475</v>
+        <v>370</v>
       </c>
       <c r="G14" t="n">
-        <v>370</v>
+        <v>265</v>
       </c>
       <c r="H14" t="n">
-        <v>265</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J14" t="n">
-        <v>105</v>
+        <v>465</v>
       </c>
       <c r="K14" t="n">
         <v>465</v>
@@ -11831,13 +11831,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="G15" t="n">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="H15" t="n">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="I15" t="n">
         <v>441</v>
@@ -11870,19 +11870,19 @@
         <v>595</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>-33</v>
       </c>
       <c r="G16" t="n">
-        <v>-33</v>
+        <v>102</v>
       </c>
       <c r="H16" t="n">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="I16" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="J16" t="n">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="K16" t="n">
         <v>317</v>
@@ -11909,13 +11909,13 @@
         <v>175</v>
       </c>
       <c r="F17" t="n">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c r="G17" t="n">
         <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="I17" t="n">
         <v>312</v>
@@ -11948,13 +11948,13 @@
         <v>1155</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>-164</v>
       </c>
       <c r="G18" t="n">
-        <v>-164</v>
+        <v>-138</v>
       </c>
       <c r="H18" t="n">
-        <v>-138</v>
+        <v>102</v>
       </c>
       <c r="I18" t="n">
         <v>102</v>
@@ -11993,7 +11993,7 @@
         <v>106</v>
       </c>
       <c r="H19" t="n">
-        <v>106</v>
+        <v>251</v>
       </c>
       <c r="I19" t="n">
         <v>251</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -449,11 +449,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -631,16 +631,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SE21029</t>
+          <t>SE21031</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 19</t>
+          <t>2,00-2,5 x 24</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>476</v>
+        <v>116</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -661,16 +661,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SE21029</t>
+          <t>SE21031</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 19</t>
+          <t>2,00-2,5 x 24</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>476</v>
+        <v>116</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -691,50 +691,50 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE21034</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>2,00-2,5 x 29</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>312</v>
+        <v>102</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE22109</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>5-8 x 57</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
@@ -751,46 +751,46 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE21032</t>
+          <t>SE21026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2,75-3,5 x 24</t>
+          <t>2,75-3,50 x 14</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE22105</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>5-8 x 37</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -801,26 +801,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE22109</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>5-8 x 57</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -836,55 +836,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE32001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2-2,50 x 9</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>243</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>IVOLUTION</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT IVOLUTIO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE24220</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>6 x 200</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>243</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -896,25 +896,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE32005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2,75-3,50 x 14</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S23</t>
         </is>
       </c>
     </row>
@@ -931,140 +931,50 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SE21040</t>
+          <t>SE21034</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 39</t>
+          <t>2,00-2,5 x 29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SE21034</t>
+          <t>SE22101</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 29</t>
+          <t>5-8 x 17</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>STENT BARE DES (SE21)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SE21041</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2,75-3,5 x 39</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>194</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>STENT BARE DES (SE21)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SE21041</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2,75-3,5 x 39</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>194</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>S23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>STENT BARE DES (SE21)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SE21041</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2,75-3,5 x 39</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>194</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S24</t>
         </is>
       </c>
     </row>
@@ -7114,10 +7024,10 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8418,25 +8328,25 @@
         <v>399</v>
       </c>
       <c r="E35" t="n">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="F35" t="n">
-        <v>-94</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>-91</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>-91</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="J35" t="n">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="K35" t="n">
-        <v>109</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36">
@@ -8496,25 +8406,25 @@
         <v>800</v>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="I37" t="n">
-        <v>-36</v>
+        <v>12</v>
       </c>
       <c r="J37" t="n">
-        <v>-32</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -8574,25 +8484,25 @@
         <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>490</v>
+        <v>294</v>
       </c>
       <c r="F39" t="n">
-        <v>153</v>
+        <v>349</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="H39" t="n">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="I39" t="n">
-        <v>255</v>
+        <v>451</v>
       </c>
       <c r="J39" t="n">
-        <v>255</v>
+        <v>451</v>
       </c>
       <c r="K39" t="n">
-        <v>255</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40">
@@ -8613,25 +8523,25 @@
         <v>800</v>
       </c>
       <c r="E40" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>-190</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>-190</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="I40" t="n">
-        <v>-182</v>
+        <v>14</v>
       </c>
       <c r="J40" t="n">
-        <v>-178</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>-174</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -8652,25 +8562,25 @@
         <v>700</v>
       </c>
       <c r="E41" t="n">
-        <v>882</v>
+        <v>392</v>
       </c>
       <c r="F41" t="n">
-        <v>-476</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>-476</v>
+        <v>14</v>
       </c>
       <c r="H41" t="n">
-        <v>224</v>
+        <v>714</v>
       </c>
       <c r="I41" t="n">
-        <v>224</v>
+        <v>714</v>
       </c>
       <c r="J41" t="n">
-        <v>224</v>
+        <v>714</v>
       </c>
       <c r="K41" t="n">
-        <v>224</v>
+        <v>714</v>
       </c>
     </row>
     <row r="42">
@@ -8691,25 +8601,25 @@
         <v>400</v>
       </c>
       <c r="E42" t="n">
-        <v>490</v>
+        <v>392</v>
       </c>
       <c r="F42" t="n">
-        <v>333</v>
+        <v>431</v>
       </c>
       <c r="G42" t="n">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="H42" t="n">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="I42" t="n">
-        <v>537</v>
+        <v>635</v>
       </c>
       <c r="J42" t="n">
-        <v>537</v>
+        <v>635</v>
       </c>
       <c r="K42" t="n">
-        <v>537</v>
+        <v>635</v>
       </c>
     </row>
     <row r="43">
@@ -8730,25 +8640,25 @@
         <v>200</v>
       </c>
       <c r="E43" t="n">
-        <v>618</v>
+        <v>422</v>
       </c>
       <c r="F43" t="n">
-        <v>-312</v>
+        <v>-116</v>
       </c>
       <c r="G43" t="n">
-        <v>-312</v>
+        <v>-116</v>
       </c>
       <c r="H43" t="n">
-        <v>-112</v>
+        <v>84</v>
       </c>
       <c r="I43" t="n">
-        <v>-112</v>
+        <v>84</v>
       </c>
       <c r="J43" t="n">
-        <v>-112</v>
+        <v>84</v>
       </c>
       <c r="K43" t="n">
-        <v>-112</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44">
@@ -8769,25 +8679,25 @@
         <v>500</v>
       </c>
       <c r="E44" t="n">
-        <v>970</v>
+        <v>578</v>
       </c>
       <c r="F44" t="n">
-        <v>37</v>
+        <v>429</v>
       </c>
       <c r="G44" t="n">
-        <v>-247</v>
+        <v>145</v>
       </c>
       <c r="H44" t="n">
-        <v>253</v>
+        <v>645</v>
       </c>
       <c r="I44" t="n">
-        <v>253</v>
+        <v>645</v>
       </c>
       <c r="J44" t="n">
-        <v>253</v>
+        <v>645</v>
       </c>
       <c r="K44" t="n">
-        <v>253</v>
+        <v>645</v>
       </c>
     </row>
     <row r="45">
@@ -8808,25 +8718,25 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>588</v>
+        <v>392</v>
       </c>
       <c r="F45" t="n">
+        <v>437</v>
+      </c>
+      <c r="G45" t="n">
         <v>241</v>
       </c>
-      <c r="G45" t="n">
-        <v>45</v>
-      </c>
       <c r="H45" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="I45" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="J45" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="K45" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46">
@@ -8847,25 +8757,25 @@
         <v>800</v>
       </c>
       <c r="E46" t="n">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="F46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G46" t="n">
         <v>-102</v>
       </c>
-      <c r="G46" t="n">
-        <v>-200</v>
-      </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I46" t="n">
-        <v>-94</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>-90</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -8886,25 +8796,25 @@
         <v>500</v>
       </c>
       <c r="E47" t="n">
-        <v>392</v>
+        <v>196</v>
       </c>
       <c r="F47" t="n">
+        <v>607</v>
+      </c>
+      <c r="G47" t="n">
         <v>411</v>
       </c>
-      <c r="G47" t="n">
-        <v>215</v>
-      </c>
       <c r="H47" t="n">
-        <v>715</v>
+        <v>911</v>
       </c>
       <c r="I47" t="n">
-        <v>715</v>
+        <v>911</v>
       </c>
       <c r="J47" t="n">
-        <v>715</v>
+        <v>911</v>
       </c>
       <c r="K47" t="n">
-        <v>715</v>
+        <v>911</v>
       </c>
     </row>
     <row r="48">
@@ -8925,25 +8835,25 @@
         <v>650</v>
       </c>
       <c r="E48" t="n">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="F48" t="n">
-        <v>199</v>
+        <v>297</v>
       </c>
       <c r="G48" t="n">
-        <v>503</v>
+        <v>601</v>
       </c>
       <c r="H48" t="n">
-        <v>503</v>
+        <v>601</v>
       </c>
       <c r="I48" t="n">
-        <v>653</v>
+        <v>751</v>
       </c>
       <c r="J48" t="n">
-        <v>653</v>
+        <v>751</v>
       </c>
       <c r="K48" t="n">
-        <v>653</v>
+        <v>751</v>
       </c>
     </row>
     <row r="49">
@@ -8964,25 +8874,25 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
       <c r="G49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
       <c r="H49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
       <c r="I49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
       <c r="J49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
       <c r="K49" t="n">
-        <v>-46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50">
@@ -9042,25 +8952,25 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>-95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -9081,25 +8991,25 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>382</v>
+        <v>98</v>
       </c>
       <c r="F52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
       <c r="G52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
       <c r="H52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
       <c r="I52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
       <c r="J52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
       <c r="K52" t="n">
-        <v>-243</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
@@ -9120,25 +9030,25 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>588</v>
+        <v>294</v>
       </c>
       <c r="F53" t="n">
+        <v>394</v>
+      </c>
+      <c r="G53" t="n">
         <v>100</v>
       </c>
-      <c r="G53" t="n">
-        <v>-194</v>
-      </c>
       <c r="H53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>-194</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
@@ -9159,25 +9069,25 @@
         <v>592</v>
       </c>
       <c r="E54" t="n">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="F54" t="n">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="G54" t="n">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="H54" t="n">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="I54" t="n">
-        <v>334</v>
+        <v>432</v>
       </c>
       <c r="J54" t="n">
-        <v>334</v>
+        <v>432</v>
       </c>
       <c r="K54" t="n">
-        <v>334</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
@@ -9237,25 +9147,25 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>442</v>
+        <v>284</v>
       </c>
       <c r="F56" t="n">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="G56" t="n">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="H56" t="n">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="I56" t="n">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="J56" t="n">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="K56" t="n">
-        <v>47</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57">
@@ -9315,25 +9225,25 @@
         <v>200</v>
       </c>
       <c r="E58" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -9354,25 +9264,25 @@
         <v>400</v>
       </c>
       <c r="E59" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F59" t="n">
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="G59" t="n">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="H59" t="n">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="I59" t="n">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="J59" t="n">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="K59" t="n">
-        <v>346</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60">
@@ -9393,25 +9303,25 @@
         <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>295</v>
+        <v>445</v>
       </c>
       <c r="G60" t="n">
-        <v>495</v>
+        <v>645</v>
       </c>
       <c r="H60" t="n">
-        <v>495</v>
+        <v>645</v>
       </c>
       <c r="I60" t="n">
-        <v>495</v>
+        <v>645</v>
       </c>
       <c r="J60" t="n">
-        <v>495</v>
+        <v>645</v>
       </c>
       <c r="K60" t="n">
-        <v>495</v>
+        <v>645</v>
       </c>
     </row>
     <row r="61">
@@ -9471,25 +9381,25 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F62" t="n">
-        <v>405</v>
+        <v>605</v>
       </c>
       <c r="G62" t="n">
-        <v>305</v>
+        <v>505</v>
       </c>
       <c r="H62" t="n">
-        <v>305</v>
+        <v>505</v>
       </c>
       <c r="I62" t="n">
-        <v>305</v>
+        <v>505</v>
       </c>
       <c r="J62" t="n">
-        <v>305</v>
+        <v>505</v>
       </c>
       <c r="K62" t="n">
-        <v>305</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63">
@@ -9510,25 +9420,25 @@
         <v>339</v>
       </c>
       <c r="E63" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="G63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="H63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="I63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="J63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="K63" t="n">
-        <v>367</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -11750,25 +11660,25 @@
         <v>1080</v>
       </c>
       <c r="E13" t="n">
-        <v>805</v>
+        <v>735</v>
       </c>
       <c r="F13" t="n">
-        <v>-59</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>-19</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
-        <v>-74</v>
+        <v>-4</v>
       </c>
       <c r="I13" t="n">
-        <v>-64</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14">
@@ -11945,25 +11855,25 @@
         <v>1125</v>
       </c>
       <c r="E18" t="n">
-        <v>1155</v>
+        <v>1050</v>
       </c>
       <c r="F18" t="n">
-        <v>-164</v>
+        <v>-59</v>
       </c>
       <c r="G18" t="n">
-        <v>-138</v>
+        <v>-33</v>
       </c>
       <c r="H18" t="n">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="I18" t="n">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="J18" t="n">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="K18" t="n">
-        <v>102</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -711,26 +711,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICOVER</t>
+          <t>ANGIOLITE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
+          <t>STENT BARE DES (SE21)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SE22109</t>
+          <t>SE21026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5-8 x 57</t>
+          <t>2,75-3,50 x 14</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -741,26 +741,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SE21026</t>
+          <t>SE22105</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 14</t>
+          <t>5-8 x 37</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SE22105</t>
+          <t>SE22109</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5-8 x 37</t>
+          <t>5-8 x 57</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -801,56 +801,56 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ICOVER</t>
+          <t>ANGIOLITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SE22109</t>
+          <t>SE32001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5-8 x 57</t>
+          <t>2-2,50 x 9</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>IVOLUTION</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
+          <t>STENT IVOLUTIO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SE32001</t>
+          <t>SE24220</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2-2,50 x 9</t>
+          <t>6 x 200</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -861,30 +861,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IVOLUTION</t>
+          <t>ANGIOLITE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STENT IVOLUTIO</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SE24220</t>
+          <t>SE32005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6 x 200</t>
+          <t>2,75-3,50 x 14</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S23</t>
         </is>
       </c>
     </row>
@@ -896,17 +896,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
+          <t>STENT BARE DES (SE21)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SE32005</t>
+          <t>SE21034</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2,75-3,50 x 14</t>
+          <t>2,00-2,5 x 29</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -914,65 +914,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>ICOVER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT BARE (SE22 ICOVER)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SE21034</t>
+          <t>SE22101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 29</t>
+          <t>5-8 x 17</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ICOVER</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SE22101</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>5-8 x 17</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>S23</t>
         </is>
@@ -9342,25 +9312,25 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>128</v>
+        <v>228</v>
       </c>
       <c r="G61" t="n">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="H61" t="n">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="I61" t="n">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="J61" t="n">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="K61" t="n">
-        <v>78</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62">
@@ -11855,25 +11825,25 @@
         <v>1125</v>
       </c>
       <c r="E18" t="n">
-        <v>1050</v>
+        <v>1015</v>
       </c>
       <c r="F18" t="n">
-        <v>-59</v>
+        <v>-24</v>
       </c>
       <c r="G18" t="n">
-        <v>-33</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="I18" t="n">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="J18" t="n">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="K18" t="n">
-        <v>207</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19">

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S24</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S22</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
         <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
         <v>53</v>
@@ -5794,7 +5794,7 @@
         <v>53</v>
       </c>
       <c r="J3" t="n">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="K3" t="n">
         <v>128</v>
@@ -5824,13 +5824,13 @@
         <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
         <v>59</v>
@@ -5860,16 +5860,16 @@
         <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="H5" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="J5" t="n">
         <v>71</v>
@@ -5899,16 +5899,16 @@
         <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="J6" t="n">
         <v>93</v>
@@ -5938,19 +5938,19 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
         <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="I7" t="n">
         <v>125</v>
       </c>
       <c r="J7" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="K7" t="n">
         <v>137</v>
@@ -5977,19 +5977,19 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
         <v>31</v>
       </c>
       <c r="J8" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -6022,13 +6022,13 @@
         <v>52</v>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I9" t="n">
         <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -6058,13 +6058,13 @@
         <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
         <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="J10" t="n">
         <v>68</v>
@@ -6097,13 +6097,13 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="J11" t="n">
         <v>70</v>
@@ -6136,13 +6136,13 @@
         <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="J12" t="n">
         <v>68</v>
@@ -6169,22 +6169,22 @@
         <v>144</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="I13" t="n">
         <v>86</v>
       </c>
       <c r="J13" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="K13" t="n">
         <v>110</v>
@@ -6211,19 +6211,19 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="J14" t="n">
-        <v>-6</v>
+        <v>57</v>
       </c>
       <c r="K14" t="n">
         <v>57</v>
@@ -6253,7 +6253,7 @@
         <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
         <v>38</v>
@@ -6262,7 +6262,7 @@
         <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="K15" t="n">
         <v>143</v>
@@ -6289,16 +6289,16 @@
         <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="J16" t="n">
         <v>53</v>
@@ -6331,13 +6331,13 @@
         <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J17" t="n">
         <v>61</v>
@@ -6367,16 +6367,16 @@
         <v>60</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="J18" t="n">
         <v>68</v>
@@ -6409,16 +6409,16 @@
         <v>73</v>
       </c>
       <c r="G19" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="I19" t="n">
         <v>121</v>
       </c>
       <c r="J19" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K19" t="n">
         <v>133</v>
@@ -6445,19 +6445,19 @@
         <v>40</v>
       </c>
       <c r="F20" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G20" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="H20" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="I20" t="n">
         <v>131</v>
       </c>
       <c r="J20" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K20" t="n">
         <v>140</v>
@@ -6496,7 +6496,7 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="K21" t="n">
         <v>129</v>
@@ -6526,16 +6526,16 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J22" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="K22" t="n">
         <v>77</v>
@@ -6562,16 +6562,16 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
         <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J23" t="n">
         <v>61</v>
@@ -6601,10 +6601,10 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="H24" t="n">
         <v>112</v>
@@ -6640,13 +6640,13 @@
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G25" t="n">
         <v>137</v>
       </c>
       <c r="H25" t="n">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="I25" t="n">
         <v>173</v>
@@ -6676,7 +6676,7 @@
         <v>105</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
@@ -6685,13 +6685,13 @@
         <v>38</v>
       </c>
       <c r="H26" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
         <v>78</v>
       </c>
       <c r="J26" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="K26" t="n">
         <v>113</v>
@@ -6718,16 +6718,16 @@
         <v>80</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
         <v>50</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="J27" t="n">
         <v>60</v>
@@ -6757,16 +6757,16 @@
         <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="H28" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I28" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J28" t="n">
         <v>63</v>
@@ -6799,7 +6799,7 @@
         <v>106</v>
       </c>
       <c r="G29" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="H29" t="n">
         <v>124</v>
@@ -6835,19 +6835,19 @@
         <v>144</v>
       </c>
       <c r="F30" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I30" t="n">
         <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="K30" t="n">
         <v>66</v>
@@ -6874,16 +6874,16 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G31" t="n">
         <v>86</v>
       </c>
       <c r="H31" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="I31" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="J31" t="n">
         <v>71</v>
@@ -6916,7 +6916,7 @@
         <v>90</v>
       </c>
       <c r="G32" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="H32" t="n">
         <v>112</v>
@@ -6955,7 +6955,7 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="H33" t="n">
         <v>104</v>
@@ -7085,19 +7085,19 @@
         <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J3" t="n">
-        <v>-15</v>
+        <v>181</v>
       </c>
       <c r="K3" t="n">
         <v>181</v>
@@ -7124,19 +7124,19 @@
         <v>270</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>202</v>
       </c>
       <c r="K4" t="n">
         <v>202</v>
@@ -7169,7 +7169,7 @@
         <v>188</v>
       </c>
       <c r="H5" t="n">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="I5" t="n">
         <v>271</v>
@@ -7202,13 +7202,13 @@
         <v>270</v>
       </c>
       <c r="F6" t="n">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -7241,16 +7241,16 @@
         <v>555</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="H7" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="J7" t="n">
         <v>89</v>
@@ -7277,22 +7277,22 @@
         <v>490</v>
       </c>
       <c r="E8" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F8" t="n">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="G8" t="n">
-        <v>247</v>
+        <v>443</v>
       </c>
       <c r="H8" t="n">
-        <v>443</v>
+        <v>203</v>
       </c>
       <c r="I8" t="n">
-        <v>203</v>
+        <v>399</v>
       </c>
       <c r="J8" t="n">
-        <v>399</v>
+        <v>497</v>
       </c>
       <c r="K8" t="n">
         <v>497</v>
@@ -7319,10 +7319,10 @@
         <v>389</v>
       </c>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -7358,16 +7358,16 @@
         <v>1050</v>
       </c>
       <c r="F10" t="n">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="H10" t="n">
-        <v>74</v>
+        <v>436</v>
       </c>
       <c r="I10" t="n">
-        <v>436</v>
+        <v>46</v>
       </c>
       <c r="J10" t="n">
         <v>46</v>
@@ -7394,22 +7394,22 @@
         <v>490</v>
       </c>
       <c r="E11" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="F11" t="n">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="G11" t="n">
         <v>360</v>
       </c>
       <c r="H11" t="n">
-        <v>360</v>
+        <v>458</v>
       </c>
       <c r="I11" t="n">
-        <v>458</v>
+        <v>226</v>
       </c>
       <c r="J11" t="n">
-        <v>226</v>
+        <v>422</v>
       </c>
       <c r="K11" t="n">
         <v>422</v>
@@ -7436,16 +7436,16 @@
         <v>735</v>
       </c>
       <c r="F12" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G12" t="n">
-        <v>182</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="J12" t="n">
         <v>72</v>
@@ -7472,22 +7472,22 @@
         <v>970</v>
       </c>
       <c r="E13" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="H13" t="n">
-        <v>241</v>
+        <v>437</v>
       </c>
       <c r="I13" t="n">
-        <v>437</v>
+        <v>250</v>
       </c>
       <c r="J13" t="n">
-        <v>250</v>
+        <v>534</v>
       </c>
       <c r="K13" t="n">
         <v>534</v>
@@ -7514,19 +7514,19 @@
         <v>390</v>
       </c>
       <c r="F14" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="H14" t="n">
-        <v>165</v>
+        <v>459</v>
       </c>
       <c r="I14" t="n">
-        <v>459</v>
+        <v>249</v>
       </c>
       <c r="J14" t="n">
-        <v>249</v>
+        <v>445</v>
       </c>
       <c r="K14" t="n">
         <v>445</v>
@@ -7553,19 +7553,19 @@
         <v>360</v>
       </c>
       <c r="F15" t="n">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="K15" t="n">
         <v>124</v>
@@ -7592,19 +7592,19 @@
         <v>150</v>
       </c>
       <c r="F16" t="n">
-        <v>186</v>
+        <v>382</v>
       </c>
       <c r="G16" t="n">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="H16" t="n">
         <v>352</v>
       </c>
       <c r="I16" t="n">
-        <v>352</v>
+        <v>232</v>
       </c>
       <c r="J16" t="n">
-        <v>232</v>
+        <v>428</v>
       </c>
       <c r="K16" t="n">
         <v>428</v>
@@ -7634,16 +7634,16 @@
         <v>380</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>478</v>
       </c>
       <c r="H17" t="n">
         <v>478</v>
       </c>
       <c r="I17" t="n">
-        <v>478</v>
+        <v>268</v>
       </c>
       <c r="J17" t="n">
-        <v>268</v>
+        <v>464</v>
       </c>
       <c r="K17" t="n">
         <v>464</v>
@@ -7670,13 +7670,13 @@
         <v>330</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="G18" t="n">
         <v>389</v>
       </c>
       <c r="H18" t="n">
-        <v>389</v>
+        <v>89</v>
       </c>
       <c r="I18" t="n">
         <v>89</v>
@@ -7712,16 +7712,16 @@
         <v>602</v>
       </c>
       <c r="G19" t="n">
-        <v>602</v>
+        <v>392</v>
       </c>
       <c r="H19" t="n">
-        <v>392</v>
+        <v>302</v>
       </c>
       <c r="I19" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="J19" t="n">
-        <v>288</v>
+        <v>386</v>
       </c>
       <c r="K19" t="n">
         <v>386</v>
@@ -7748,7 +7748,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
         <v>12</v>
@@ -7790,13 +7790,13 @@
         <v>228</v>
       </c>
       <c r="G21" t="n">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="H21" t="n">
-        <v>512</v>
+        <v>182</v>
       </c>
       <c r="I21" t="n">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="J21" t="n">
         <v>280</v>
@@ -7826,10 +7826,10 @@
         <v>510</v>
       </c>
       <c r="F22" t="n">
-        <v>223</v>
+        <v>321</v>
       </c>
       <c r="G22" t="n">
-        <v>321</v>
+        <v>517</v>
       </c>
       <c r="H22" t="n">
         <v>517</v>
@@ -7838,7 +7838,7 @@
         <v>517</v>
       </c>
       <c r="J22" t="n">
-        <v>517</v>
+        <v>301</v>
       </c>
       <c r="K22" t="n">
         <v>301</v>
@@ -7868,13 +7868,13 @@
         <v>207</v>
       </c>
       <c r="G23" t="n">
-        <v>207</v>
+        <v>305</v>
       </c>
       <c r="H23" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="I23" t="n">
-        <v>290</v>
+        <v>486</v>
       </c>
       <c r="J23" t="n">
         <v>486</v>
@@ -7904,19 +7904,19 @@
         <v>420</v>
       </c>
       <c r="F24" t="n">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="G24" t="n">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="H24" t="n">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="I24" t="n">
-        <v>172</v>
+        <v>368</v>
       </c>
       <c r="J24" t="n">
-        <v>368</v>
+        <v>248</v>
       </c>
       <c r="K24" t="n">
         <v>248</v>
@@ -7943,19 +7943,19 @@
         <v>450</v>
       </c>
       <c r="F25" t="n">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="G25" t="n">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="I25" t="n">
-        <v>166</v>
+        <v>254</v>
       </c>
       <c r="J25" t="n">
-        <v>254</v>
+        <v>352</v>
       </c>
       <c r="K25" t="n">
         <v>352</v>
@@ -7982,16 +7982,16 @@
         <v>210</v>
       </c>
       <c r="F26" t="n">
-        <v>576</v>
+        <v>516</v>
       </c>
       <c r="G26" t="n">
-        <v>516</v>
+        <v>366</v>
       </c>
       <c r="H26" t="n">
         <v>366</v>
       </c>
       <c r="I26" t="n">
-        <v>366</v>
+        <v>562</v>
       </c>
       <c r="J26" t="n">
         <v>562</v>
@@ -8024,7 +8024,7 @@
         <v>70</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H27" t="n">
         <v>120</v>
@@ -8033,7 +8033,7 @@
         <v>120</v>
       </c>
       <c r="J27" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K27" t="n">
         <v>160</v>
@@ -8060,19 +8060,19 @@
         <v>240</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I28" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J28" t="n">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="K28" t="n">
         <v>129</v>
@@ -8099,16 +8099,16 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G29" t="n">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="H29" t="n">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="I29" t="n">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="J29" t="n">
         <v>259</v>
@@ -8138,19 +8138,19 @@
         <v>210</v>
       </c>
       <c r="F30" t="n">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="G30" t="n">
         <v>93</v>
       </c>
       <c r="H30" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="I30" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="J30" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="K30" t="n">
         <v>113</v>
@@ -8177,19 +8177,19 @@
         <v>360</v>
       </c>
       <c r="F31" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G31" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H31" t="n">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="I31" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="J31" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="K31" t="n">
         <v>112</v>
@@ -8219,13 +8219,13 @@
         <v>108</v>
       </c>
       <c r="G32" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="H32" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I32" t="n">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="J32" t="n">
         <v>138</v>
@@ -9605,7 +9605,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G5" t="n">
         <v>124</v>
@@ -9761,7 +9761,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="G9" t="n">
         <v>111</v>
@@ -9800,10 +9800,10 @@
         <v>118</v>
       </c>
       <c r="F10" t="n">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="H10" t="n">
         <v>149</v>
@@ -9839,7 +9839,7 @@
         <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="G11" t="n">
         <v>109</v>
@@ -9878,7 +9878,7 @@
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="G12" t="n">
         <v>104</v>
@@ -9890,7 +9890,7 @@
         <v>104</v>
       </c>
       <c r="J12" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="K12" t="n">
         <v>152</v>
@@ -9956,7 +9956,7 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -9968,7 +9968,7 @@
         <v>93</v>
       </c>
       <c r="J14" t="n">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="K14" t="n">
         <v>189</v>
@@ -9998,13 +9998,13 @@
         <v>164</v>
       </c>
       <c r="G15" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="H15" t="n">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="I15" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="J15" t="n">
         <v>253</v>
@@ -10073,13 +10073,13 @@
         <v>195</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="I17" t="n">
         <v>156</v>
@@ -10124,7 +10124,7 @@
         <v>103</v>
       </c>
       <c r="J18" t="n">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="K18" t="n">
         <v>151</v>
@@ -10154,7 +10154,7 @@
         <v>134</v>
       </c>
       <c r="G19" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="H19" t="n">
         <v>104</v>
@@ -10163,7 +10163,7 @@
         <v>104</v>
       </c>
       <c r="J19" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="K19" t="n">
         <v>152</v>
@@ -10193,13 +10193,13 @@
         <v>107</v>
       </c>
       <c r="G20" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H20" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="I20" t="n">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="J20" t="n">
         <v>183</v>
@@ -10235,7 +10235,7 @@
         <v>105</v>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I21" t="n">
         <v>111</v>
@@ -10268,7 +10268,7 @@
         <v>360</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G22" t="n">
         <v>99</v>
@@ -10277,10 +10277,10 @@
         <v>99</v>
       </c>
       <c r="I22" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="J22" t="n">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="K22" t="n">
         <v>171</v>
@@ -10349,10 +10349,10 @@
         <v>98</v>
       </c>
       <c r="G24" t="n">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="H24" t="n">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="I24" t="n">
         <v>116</v>
@@ -10385,13 +10385,13 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="G25" t="n">
         <v>142</v>
       </c>
       <c r="H25" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="I25" t="n">
         <v>112</v>
@@ -10430,7 +10430,7 @@
         <v>132</v>
       </c>
       <c r="H26" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="I26" t="n">
         <v>102</v>
@@ -10463,19 +10463,19 @@
         <v>390</v>
       </c>
       <c r="F27" t="n">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="G27" t="n">
         <v>221</v>
       </c>
       <c r="H27" t="n">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I27" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="J27" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -10596,7 +10596,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="G3" t="n">
         <v>142</v>
@@ -10632,16 +10632,16 @@
         <v>250</v>
       </c>
       <c r="E4" t="n">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="I4" t="n">
         <v>199</v>
@@ -10674,13 +10674,13 @@
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
         <v>103</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="I5" t="n">
         <v>233</v>
@@ -10752,10 +10752,10 @@
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>66</v>
+        <v>196</v>
       </c>
       <c r="H7" t="n">
         <v>196</v>
@@ -10791,10 +10791,10 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="G8" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H8" t="n">
         <v>94</v>
@@ -10833,7 +10833,7 @@
         <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="H9" t="n">
         <v>176</v>
@@ -10869,10 +10869,10 @@
         <v>120</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -10911,7 +10911,7 @@
         <v>144</v>
       </c>
       <c r="G11" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
         <v>114</v>
@@ -10947,13 +10947,13 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
         <v>61</v>
       </c>
       <c r="H12" t="n">
-        <v>61</v>
+        <v>191</v>
       </c>
       <c r="I12" t="n">
         <v>191</v>
@@ -10989,7 +10989,7 @@
         <v>110</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
         <v>20</v>
@@ -11022,13 +11022,13 @@
         <v>130</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="H14" t="n">
         <v>205</v>
@@ -11275,19 +11275,19 @@
         <v>507</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="I3" t="n">
-        <v>226</v>
+        <v>41</v>
       </c>
       <c r="J3" t="n">
-        <v>41</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
         <v>361</v>
@@ -11314,19 +11314,19 @@
         <v>907</v>
       </c>
       <c r="F4" t="n">
-        <v>773</v>
+        <v>696</v>
       </c>
       <c r="G4" t="n">
-        <v>696</v>
+        <v>631</v>
       </c>
       <c r="H4" t="n">
-        <v>631</v>
+        <v>526</v>
       </c>
       <c r="I4" t="n">
-        <v>526</v>
+        <v>426</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>776</v>
       </c>
       <c r="K4" t="n">
         <v>776</v>
@@ -11353,10 +11353,10 @@
         <v>225</v>
       </c>
       <c r="F5" t="n">
-        <v>1287</v>
+        <v>1227</v>
       </c>
       <c r="G5" t="n">
-        <v>1227</v>
+        <v>1212</v>
       </c>
       <c r="H5" t="n">
         <v>1212</v>
@@ -11365,7 +11365,7 @@
         <v>1212</v>
       </c>
       <c r="J5" t="n">
-        <v>1212</v>
+        <v>1062</v>
       </c>
       <c r="K5" t="n">
         <v>1062</v>
@@ -11392,19 +11392,19 @@
         <v>485</v>
       </c>
       <c r="F6" t="n">
-        <v>691</v>
+        <v>656</v>
       </c>
       <c r="G6" t="n">
-        <v>656</v>
+        <v>431</v>
       </c>
       <c r="H6" t="n">
-        <v>431</v>
+        <v>536</v>
       </c>
       <c r="I6" t="n">
-        <v>536</v>
+        <v>711</v>
       </c>
       <c r="J6" t="n">
-        <v>711</v>
+        <v>801</v>
       </c>
       <c r="K6" t="n">
         <v>801</v>
@@ -11431,16 +11431,16 @@
         <v>382</v>
       </c>
       <c r="F7" t="n">
-        <v>1217</v>
+        <v>1072</v>
       </c>
       <c r="G7" t="n">
-        <v>1072</v>
+        <v>1045</v>
       </c>
       <c r="H7" t="n">
-        <v>1045</v>
+        <v>835</v>
       </c>
       <c r="I7" t="n">
-        <v>835</v>
+        <v>1010</v>
       </c>
       <c r="J7" t="n">
         <v>1010</v>
@@ -11470,19 +11470,19 @@
         <v>750</v>
       </c>
       <c r="F8" t="n">
-        <v>569</v>
+        <v>339</v>
       </c>
       <c r="G8" t="n">
-        <v>339</v>
+        <v>654</v>
       </c>
       <c r="H8" t="n">
-        <v>654</v>
+        <v>1034</v>
       </c>
       <c r="I8" t="n">
         <v>1034</v>
       </c>
       <c r="J8" t="n">
-        <v>1034</v>
+        <v>974</v>
       </c>
       <c r="K8" t="n">
         <v>974</v>
@@ -11509,16 +11509,16 @@
         <v>510</v>
       </c>
       <c r="F9" t="n">
-        <v>1462</v>
+        <v>1402</v>
       </c>
       <c r="G9" t="n">
-        <v>1402</v>
+        <v>1342</v>
       </c>
       <c r="H9" t="n">
-        <v>1342</v>
+        <v>1042</v>
       </c>
       <c r="I9" t="n">
-        <v>1042</v>
+        <v>987</v>
       </c>
       <c r="J9" t="n">
         <v>987</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>20</v>
@@ -12124,7 +12124,7 @@
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
@@ -12199,13 +12199,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -12244,7 +12244,7 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J7" t="n">
         <v>35</v>
@@ -12280,10 +12280,10 @@
         <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J8" t="n">
         <v>85</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,55 +626,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE32001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>2-2,50 x 9</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANGIOLITE</t>
+          <t>IVOLUTION</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT IVOLUTIO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SE21031</t>
+          <t>SE24220</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 24</t>
+          <t>6 x 200</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S25</t>
         </is>
       </c>
     </row>
@@ -686,263 +686,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STENT BARE DES (SE21)</t>
+          <t>STENT RECUBIERTO DES (SE32)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SE21034</t>
+          <t>SE32005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,00-2,5 x 29</t>
+          <t>2,75-3,50 x 14</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>STENT BARE DES (SE21)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SE21026</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2,75-3,50 x 14</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>42</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ICOVER</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SE22105</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5-8 x 37</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>33</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ICOVER</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SE22109</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5-8 x 57</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>24</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SE32001</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2-2,50 x 9</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IVOLUTION</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>STENT IVOLUTIO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SE24220</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6 x 200</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>STENT RECUBIERTO DES (SE32)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SE32005</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2,75-3,50 x 14</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S22</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ANGIOLITE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>STENT BARE DES (SE21)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SE21034</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2,00-2,5 x 29</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S21</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ICOVER</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>STENT BARE (SE22 ICOVER)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SE22101</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5-8 x 17</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>S23</t>
         </is>
@@ -5782,7 +5542,7 @@
         <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
         <v>53</v>
@@ -5794,7 +5554,7 @@
         <v>53</v>
       </c>
       <c r="J3" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="K3" t="n">
         <v>128</v>
@@ -5824,13 +5584,13 @@
         <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>59</v>
@@ -5860,16 +5620,16 @@
         <v>70</v>
       </c>
       <c r="F5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G5" t="n">
         <v>13</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>57</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>27</v>
-      </c>
-      <c r="I5" t="n">
-        <v>71</v>
       </c>
       <c r="J5" t="n">
         <v>71</v>
@@ -5899,16 +5659,16 @@
         <v>120</v>
       </c>
       <c r="F6" t="n">
+        <v>69</v>
+      </c>
+      <c r="G6" t="n">
         <v>49</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>45</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>93</v>
       </c>
       <c r="J6" t="n">
         <v>93</v>
@@ -5938,19 +5698,19 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
         <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="I7" t="n">
         <v>125</v>
       </c>
       <c r="J7" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K7" t="n">
         <v>137</v>
@@ -5977,19 +5737,19 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
         <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
         <v>31</v>
       </c>
       <c r="J8" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -6022,13 +5782,13 @@
         <v>52</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I9" t="n">
         <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
         <v>147</v>
@@ -6058,13 +5818,13 @@
         <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
         <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
         <v>68</v>
@@ -6097,13 +5857,13 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>70</v>
@@ -6136,13 +5896,13 @@
         <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>68</v>
@@ -6169,22 +5929,22 @@
         <v>144</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>86</v>
       </c>
       <c r="J13" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="K13" t="n">
         <v>110</v>
@@ -6211,19 +5971,19 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
       </c>
       <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>57</v>
       </c>
       <c r="K14" t="n">
         <v>57</v>
@@ -6253,7 +6013,7 @@
         <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="H15" t="n">
         <v>38</v>
@@ -6262,7 +6022,7 @@
         <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
         <v>143</v>
@@ -6289,16 +6049,16 @@
         <v>50</v>
       </c>
       <c r="F16" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" t="n">
         <v>18</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>13</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>53</v>
       </c>
       <c r="J16" t="n">
         <v>53</v>
@@ -6331,13 +6091,13 @@
         <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
         <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
         <v>61</v>
@@ -6367,16 +6127,16 @@
         <v>60</v>
       </c>
       <c r="F18" t="n">
+        <v>56</v>
+      </c>
+      <c r="G18" t="n">
         <v>46</v>
-      </c>
-      <c r="G18" t="n">
-        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
         <v>68</v>
@@ -6409,16 +6169,16 @@
         <v>73</v>
       </c>
       <c r="G19" t="n">
+        <v>73</v>
+      </c>
+      <c r="H19" t="n">
         <v>13</v>
-      </c>
-      <c r="H19" t="n">
-        <v>121</v>
       </c>
       <c r="I19" t="n">
         <v>121</v>
       </c>
       <c r="J19" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K19" t="n">
         <v>133</v>
@@ -6445,19 +6205,19 @@
         <v>40</v>
       </c>
       <c r="F20" t="n">
+        <v>144</v>
+      </c>
+      <c r="G20" t="n">
         <v>153</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>113</v>
-      </c>
-      <c r="H20" t="n">
-        <v>131</v>
       </c>
       <c r="I20" t="n">
         <v>131</v>
       </c>
       <c r="J20" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K20" t="n">
         <v>140</v>
@@ -6496,7 +6256,7 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
         <v>129</v>
@@ -6526,16 +6286,16 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>52</v>
-      </c>
-      <c r="J22" t="n">
-        <v>77</v>
       </c>
       <c r="K22" t="n">
         <v>77</v>
@@ -6562,16 +6322,16 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" t="n">
         <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>17</v>
       </c>
       <c r="H23" t="n">
         <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
         <v>61</v>
@@ -6601,10 +6361,10 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
+        <v>96</v>
+      </c>
+      <c r="G24" t="n">
         <v>76</v>
-      </c>
-      <c r="G24" t="n">
-        <v>112</v>
       </c>
       <c r="H24" t="n">
         <v>112</v>
@@ -6640,13 +6400,13 @@
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G25" t="n">
         <v>137</v>
       </c>
       <c r="H25" t="n">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="I25" t="n">
         <v>173</v>
@@ -6676,7 +6436,7 @@
         <v>105</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
@@ -6685,13 +6445,13 @@
         <v>38</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="I26" t="n">
         <v>78</v>
       </c>
       <c r="J26" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K26" t="n">
         <v>113</v>
@@ -6718,16 +6478,16 @@
         <v>80</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G27" t="n">
         <v>50</v>
       </c>
       <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="n">
         <v>10</v>
-      </c>
-      <c r="I27" t="n">
-        <v>60</v>
       </c>
       <c r="J27" t="n">
         <v>60</v>
@@ -6757,16 +6517,16 @@
         <v>50</v>
       </c>
       <c r="F28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G28" t="n">
         <v>29</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>51</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>41</v>
-      </c>
-      <c r="I28" t="n">
-        <v>63</v>
       </c>
       <c r="J28" t="n">
         <v>63</v>
@@ -6799,7 +6559,7 @@
         <v>106</v>
       </c>
       <c r="G29" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H29" t="n">
         <v>124</v>
@@ -6835,19 +6595,19 @@
         <v>144</v>
       </c>
       <c r="F30" t="n">
+        <v>73</v>
+      </c>
+      <c r="G30" t="n">
         <v>34</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>24</v>
-      </c>
-      <c r="H30" t="n">
-        <v>31</v>
       </c>
       <c r="I30" t="n">
         <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
         <v>66</v>
@@ -6874,16 +6634,16 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G31" t="n">
         <v>86</v>
       </c>
       <c r="H31" t="n">
+        <v>86</v>
+      </c>
+      <c r="I31" t="n">
         <v>46</v>
-      </c>
-      <c r="I31" t="n">
-        <v>71</v>
       </c>
       <c r="J31" t="n">
         <v>71</v>
@@ -6916,7 +6676,7 @@
         <v>90</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="H32" t="n">
         <v>112</v>
@@ -6955,7 +6715,7 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="H33" t="n">
         <v>104</v>
@@ -6992,12 +6752,12 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7085,19 +6845,19 @@
         <v>195</v>
       </c>
       <c r="F3" t="n">
+        <v>82</v>
+      </c>
+      <c r="G3" t="n">
         <v>67</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>-15</v>
-      </c>
-      <c r="J3" t="n">
-        <v>181</v>
       </c>
       <c r="K3" t="n">
         <v>181</v>
@@ -7124,19 +6884,19 @@
         <v>270</v>
       </c>
       <c r="F4" t="n">
+        <v>130</v>
+      </c>
+      <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>18</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>202</v>
@@ -7169,7 +6929,7 @@
         <v>188</v>
       </c>
       <c r="H5" t="n">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="I5" t="n">
         <v>271</v>
@@ -7202,13 +6962,13 @@
         <v>270</v>
       </c>
       <c r="F6" t="n">
+        <v>228</v>
+      </c>
+      <c r="G6" t="n">
         <v>108</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>36</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -7241,16 +7001,16 @@
         <v>555</v>
       </c>
       <c r="F7" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" t="n">
         <v>16</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>89</v>
       </c>
       <c r="J7" t="n">
         <v>89</v>
@@ -7277,22 +7037,22 @@
         <v>490</v>
       </c>
       <c r="E8" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F8" t="n">
+        <v>282</v>
+      </c>
+      <c r="G8" t="n">
         <v>247</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>443</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>203</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>399</v>
-      </c>
-      <c r="J8" t="n">
-        <v>497</v>
       </c>
       <c r="K8" t="n">
         <v>497</v>
@@ -7319,10 +7079,10 @@
         <v>389</v>
       </c>
       <c r="F9" t="n">
+        <v>207</v>
+      </c>
+      <c r="G9" t="n">
         <v>13</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -7358,16 +7118,16 @@
         <v>1050</v>
       </c>
       <c r="F10" t="n">
+        <v>214</v>
+      </c>
+      <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>74</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>436</v>
-      </c>
-      <c r="I10" t="n">
-        <v>46</v>
       </c>
       <c r="J10" t="n">
         <v>46</v>
@@ -7394,22 +7154,22 @@
         <v>490</v>
       </c>
       <c r="E11" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="F11" t="n">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="G11" t="n">
         <v>360</v>
       </c>
       <c r="H11" t="n">
+        <v>360</v>
+      </c>
+      <c r="I11" t="n">
         <v>458</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>226</v>
-      </c>
-      <c r="J11" t="n">
-        <v>422</v>
       </c>
       <c r="K11" t="n">
         <v>422</v>
@@ -7436,16 +7196,16 @@
         <v>735</v>
       </c>
       <c r="F12" t="n">
+        <v>189</v>
+      </c>
+      <c r="G12" t="n">
         <v>182</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>26</v>
-      </c>
-      <c r="I12" t="n">
-        <v>72</v>
       </c>
       <c r="J12" t="n">
         <v>72</v>
@@ -7472,22 +7232,22 @@
         <v>970</v>
       </c>
       <c r="E13" t="n">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
         <v>45</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>241</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>437</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>250</v>
-      </c>
-      <c r="J13" t="n">
-        <v>534</v>
       </c>
       <c r="K13" t="n">
         <v>534</v>
@@ -7514,19 +7274,19 @@
         <v>390</v>
       </c>
       <c r="F14" t="n">
+        <v>247</v>
+      </c>
+      <c r="G14" t="n">
         <v>255</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>165</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>459</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>249</v>
-      </c>
-      <c r="J14" t="n">
-        <v>445</v>
       </c>
       <c r="K14" t="n">
         <v>445</v>
@@ -7553,19 +7313,19 @@
         <v>360</v>
       </c>
       <c r="F15" t="n">
+        <v>190</v>
+      </c>
+      <c r="G15" t="n">
         <v>10</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>18</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>26</v>
-      </c>
-      <c r="J15" t="n">
-        <v>124</v>
       </c>
       <c r="K15" t="n">
         <v>124</v>
@@ -7592,19 +7352,19 @@
         <v>150</v>
       </c>
       <c r="F16" t="n">
+        <v>186</v>
+      </c>
+      <c r="G16" t="n">
         <v>382</v>
-      </c>
-      <c r="G16" t="n">
-        <v>352</v>
       </c>
       <c r="H16" t="n">
         <v>352</v>
       </c>
       <c r="I16" t="n">
+        <v>352</v>
+      </c>
+      <c r="J16" t="n">
         <v>232</v>
-      </c>
-      <c r="J16" t="n">
-        <v>428</v>
       </c>
       <c r="K16" t="n">
         <v>428</v>
@@ -7634,16 +7394,16 @@
         <v>380</v>
       </c>
       <c r="G17" t="n">
-        <v>478</v>
+        <v>380</v>
       </c>
       <c r="H17" t="n">
         <v>478</v>
       </c>
       <c r="I17" t="n">
+        <v>478</v>
+      </c>
+      <c r="J17" t="n">
         <v>268</v>
-      </c>
-      <c r="J17" t="n">
-        <v>464</v>
       </c>
       <c r="K17" t="n">
         <v>464</v>
@@ -7670,13 +7430,13 @@
         <v>330</v>
       </c>
       <c r="F18" t="n">
-        <v>389</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>389</v>
       </c>
       <c r="H18" t="n">
-        <v>89</v>
+        <v>389</v>
       </c>
       <c r="I18" t="n">
         <v>89</v>
@@ -7712,16 +7472,16 @@
         <v>602</v>
       </c>
       <c r="G19" t="n">
+        <v>602</v>
+      </c>
+      <c r="H19" t="n">
         <v>392</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>302</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>288</v>
-      </c>
-      <c r="J19" t="n">
-        <v>386</v>
       </c>
       <c r="K19" t="n">
         <v>386</v>
@@ -7748,7 +7508,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
         <v>12</v>
@@ -7790,13 +7550,13 @@
         <v>228</v>
       </c>
       <c r="G21" t="n">
+        <v>228</v>
+      </c>
+      <c r="H21" t="n">
         <v>512</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>182</v>
-      </c>
-      <c r="I21" t="n">
-        <v>280</v>
       </c>
       <c r="J21" t="n">
         <v>280</v>
@@ -7826,10 +7586,10 @@
         <v>510</v>
       </c>
       <c r="F22" t="n">
+        <v>223</v>
+      </c>
+      <c r="G22" t="n">
         <v>321</v>
-      </c>
-      <c r="G22" t="n">
-        <v>517</v>
       </c>
       <c r="H22" t="n">
         <v>517</v>
@@ -7838,7 +7598,7 @@
         <v>517</v>
       </c>
       <c r="J22" t="n">
-        <v>301</v>
+        <v>517</v>
       </c>
       <c r="K22" t="n">
         <v>301</v>
@@ -7868,13 +7628,13 @@
         <v>207</v>
       </c>
       <c r="G23" t="n">
+        <v>207</v>
+      </c>
+      <c r="H23" t="n">
         <v>305</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>290</v>
-      </c>
-      <c r="I23" t="n">
-        <v>486</v>
       </c>
       <c r="J23" t="n">
         <v>486</v>
@@ -7904,19 +7664,19 @@
         <v>420</v>
       </c>
       <c r="F24" t="n">
+        <v>374</v>
+      </c>
+      <c r="G24" t="n">
         <v>314</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>284</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>172</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>368</v>
-      </c>
-      <c r="J24" t="n">
-        <v>248</v>
       </c>
       <c r="K24" t="n">
         <v>248</v>
@@ -7943,19 +7703,19 @@
         <v>450</v>
       </c>
       <c r="F25" t="n">
+        <v>360</v>
+      </c>
+      <c r="G25" t="n">
         <v>428</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>8</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>166</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>254</v>
-      </c>
-      <c r="J25" t="n">
-        <v>352</v>
       </c>
       <c r="K25" t="n">
         <v>352</v>
@@ -7982,16 +7742,16 @@
         <v>210</v>
       </c>
       <c r="F26" t="n">
+        <v>576</v>
+      </c>
+      <c r="G26" t="n">
         <v>516</v>
-      </c>
-      <c r="G26" t="n">
-        <v>366</v>
       </c>
       <c r="H26" t="n">
         <v>366</v>
       </c>
       <c r="I26" t="n">
-        <v>562</v>
+        <v>366</v>
       </c>
       <c r="J26" t="n">
         <v>562</v>
@@ -8024,7 +7784,7 @@
         <v>70</v>
       </c>
       <c r="G27" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H27" t="n">
         <v>120</v>
@@ -8033,7 +7793,7 @@
         <v>120</v>
       </c>
       <c r="J27" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="K27" t="n">
         <v>160</v>
@@ -8060,19 +7820,19 @@
         <v>240</v>
       </c>
       <c r="F28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G28" t="n">
         <v>9</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>49</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>39</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>59</v>
-      </c>
-      <c r="J28" t="n">
-        <v>129</v>
       </c>
       <c r="K28" t="n">
         <v>129</v>
@@ -8099,16 +7859,16 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
+        <v>89</v>
+      </c>
+      <c r="G29" t="n">
         <v>59</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>159</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>209</v>
-      </c>
-      <c r="I29" t="n">
-        <v>259</v>
       </c>
       <c r="J29" t="n">
         <v>259</v>
@@ -8138,19 +7898,19 @@
         <v>210</v>
       </c>
       <c r="F30" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G30" t="n">
         <v>93</v>
       </c>
       <c r="H30" t="n">
+        <v>93</v>
+      </c>
+      <c r="I30" t="n">
         <v>73</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>123</v>
-      </c>
-      <c r="J30" t="n">
-        <v>113</v>
       </c>
       <c r="K30" t="n">
         <v>113</v>
@@ -8177,19 +7937,19 @@
         <v>360</v>
       </c>
       <c r="F31" t="n">
+        <v>72</v>
+      </c>
+      <c r="G31" t="n">
         <v>92</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>102</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>32</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>132</v>
-      </c>
-      <c r="J31" t="n">
-        <v>112</v>
       </c>
       <c r="K31" t="n">
         <v>112</v>
@@ -8219,13 +7979,13 @@
         <v>108</v>
       </c>
       <c r="G32" t="n">
+        <v>108</v>
+      </c>
+      <c r="H32" t="n">
         <v>18</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>38</v>
-      </c>
-      <c r="I32" t="n">
-        <v>138</v>
       </c>
       <c r="J32" t="n">
         <v>138</v>
@@ -8259,25 +8019,25 @@
         <v>199</v>
       </c>
       <c r="E34" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="I34" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35">
@@ -8298,25 +8058,25 @@
         <v>399</v>
       </c>
       <c r="E35" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="I35" t="n">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="J35" t="n">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="K35" t="n">
-        <v>207</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36">
@@ -8337,25 +8097,25 @@
         <v>549</v>
       </c>
       <c r="E36" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="G36" t="n">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="H36" t="n">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="I36" t="n">
-        <v>627</v>
+        <v>176</v>
       </c>
       <c r="J36" t="n">
-        <v>627</v>
+        <v>375</v>
       </c>
       <c r="K36" t="n">
-        <v>627</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37">
@@ -8385,16 +8145,16 @@
         <v>4</v>
       </c>
       <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="n">
         <v>204</v>
-      </c>
-      <c r="I37" t="n">
-        <v>12</v>
-      </c>
-      <c r="J37" t="n">
-        <v>16</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -8415,25 +8175,25 @@
         <v>550</v>
       </c>
       <c r="E38" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-42</v>
+        <v>546</v>
       </c>
       <c r="G38" t="n">
-        <v>108</v>
+        <v>546</v>
       </c>
       <c r="H38" t="n">
-        <v>108</v>
+        <v>546</v>
       </c>
       <c r="I38" t="n">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="J38" t="n">
-        <v>508</v>
+        <v>696</v>
       </c>
       <c r="K38" t="n">
-        <v>508</v>
+        <v>696</v>
       </c>
     </row>
     <row r="39">
@@ -8454,25 +8214,25 @@
         <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>349</v>
+        <v>545</v>
       </c>
       <c r="G39" t="n">
-        <v>251</v>
+        <v>545</v>
       </c>
       <c r="H39" t="n">
-        <v>251</v>
+        <v>545</v>
       </c>
       <c r="I39" t="n">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="J39" t="n">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="K39" t="n">
-        <v>451</v>
+        <v>545</v>
       </c>
     </row>
     <row r="40">
@@ -8502,16 +8262,16 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" t="n">
         <v>206</v>
-      </c>
-      <c r="I40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J40" t="n">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -8532,25 +8292,25 @@
         <v>700</v>
       </c>
       <c r="E41" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>406</v>
       </c>
       <c r="G41" t="n">
-        <v>14</v>
+        <v>406</v>
       </c>
       <c r="H41" t="n">
-        <v>714</v>
+        <v>406</v>
       </c>
       <c r="I41" t="n">
-        <v>714</v>
+        <v>406</v>
       </c>
       <c r="J41" t="n">
-        <v>714</v>
+        <v>406</v>
       </c>
       <c r="K41" t="n">
-        <v>714</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="42">
@@ -8571,25 +8331,25 @@
         <v>400</v>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>431</v>
+        <v>627</v>
       </c>
       <c r="G42" t="n">
-        <v>235</v>
+        <v>627</v>
       </c>
       <c r="H42" t="n">
-        <v>235</v>
+        <v>627</v>
       </c>
       <c r="I42" t="n">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="J42" t="n">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="K42" t="n">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="43">
@@ -8610,25 +8370,25 @@
         <v>200</v>
       </c>
       <c r="E43" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>-116</v>
+        <v>306</v>
       </c>
       <c r="G43" t="n">
-        <v>-116</v>
+        <v>306</v>
       </c>
       <c r="H43" t="n">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="I43" t="n">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="J43" t="n">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="K43" t="n">
-        <v>84</v>
+        <v>506</v>
       </c>
     </row>
     <row r="44">
@@ -8649,25 +8409,25 @@
         <v>500</v>
       </c>
       <c r="E44" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>429</v>
+        <v>723</v>
       </c>
       <c r="G44" t="n">
-        <v>145</v>
+        <v>723</v>
       </c>
       <c r="H44" t="n">
-        <v>645</v>
+        <v>723</v>
       </c>
       <c r="I44" t="n">
-        <v>645</v>
+        <v>723</v>
       </c>
       <c r="J44" t="n">
-        <v>645</v>
+        <v>723</v>
       </c>
       <c r="K44" t="n">
-        <v>645</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="45">
@@ -8688,25 +8448,25 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>437</v>
+        <v>633</v>
       </c>
       <c r="G45" t="n">
-        <v>241</v>
+        <v>633</v>
       </c>
       <c r="H45" t="n">
-        <v>241</v>
+        <v>633</v>
       </c>
       <c r="I45" t="n">
-        <v>241</v>
+        <v>633</v>
       </c>
       <c r="J45" t="n">
-        <v>241</v>
+        <v>633</v>
       </c>
       <c r="K45" t="n">
-        <v>241</v>
+        <v>633</v>
       </c>
     </row>
     <row r="46">
@@ -8727,25 +8487,25 @@
         <v>800</v>
       </c>
       <c r="E46" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-4</v>
+        <v>94</v>
       </c>
       <c r="G46" t="n">
-        <v>-102</v>
+        <v>94</v>
       </c>
       <c r="H46" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47">
@@ -8766,25 +8526,25 @@
         <v>500</v>
       </c>
       <c r="E47" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>607</v>
       </c>
       <c r="G47" t="n">
-        <v>411</v>
+        <v>607</v>
       </c>
       <c r="H47" t="n">
-        <v>911</v>
+        <v>607</v>
       </c>
       <c r="I47" t="n">
-        <v>911</v>
+        <v>607</v>
       </c>
       <c r="J47" t="n">
-        <v>911</v>
+        <v>607</v>
       </c>
       <c r="K47" t="n">
-        <v>911</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="48">
@@ -8805,25 +8565,25 @@
         <v>650</v>
       </c>
       <c r="E48" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>297</v>
       </c>
       <c r="G48" t="n">
-        <v>601</v>
+        <v>297</v>
       </c>
       <c r="H48" t="n">
-        <v>601</v>
+        <v>297</v>
       </c>
       <c r="I48" t="n">
-        <v>751</v>
+        <v>297</v>
       </c>
       <c r="J48" t="n">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="K48" t="n">
-        <v>751</v>
+        <v>797</v>
       </c>
     </row>
     <row r="49">
@@ -8883,25 +8643,25 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>547</v>
+        <v>743</v>
       </c>
       <c r="G50" t="n">
-        <v>449</v>
+        <v>743</v>
       </c>
       <c r="H50" t="n">
-        <v>449</v>
+        <v>743</v>
       </c>
       <c r="I50" t="n">
-        <v>449</v>
+        <v>743</v>
       </c>
       <c r="J50" t="n">
-        <v>449</v>
+        <v>743</v>
       </c>
       <c r="K50" t="n">
-        <v>449</v>
+        <v>743</v>
       </c>
     </row>
     <row r="51">
@@ -8961,25 +8721,25 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="G52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="I52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="J52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="K52" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53">
@@ -9000,25 +8760,25 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>394</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="I53" t="n">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54">
@@ -9039,25 +8799,25 @@
         <v>592</v>
       </c>
       <c r="E54" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="G54" t="n">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="H54" t="n">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="I54" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J54" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="K54" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55">
@@ -9078,25 +8838,25 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="G55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="H55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="I55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="J55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="K55" t="n">
-        <v>41</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56">
@@ -9117,25 +8877,25 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>303</v>
+        <v>489</v>
       </c>
       <c r="G56" t="n">
-        <v>205</v>
+        <v>489</v>
       </c>
       <c r="H56" t="n">
-        <v>205</v>
+        <v>489</v>
       </c>
       <c r="I56" t="n">
-        <v>205</v>
+        <v>489</v>
       </c>
       <c r="J56" t="n">
-        <v>205</v>
+        <v>489</v>
       </c>
       <c r="K56" t="n">
-        <v>205</v>
+        <v>489</v>
       </c>
     </row>
     <row r="57">
@@ -9156,25 +8916,25 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="G57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="H57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="I57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="J57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
       <c r="K57" t="n">
-        <v>461</v>
+        <v>657</v>
       </c>
     </row>
     <row r="58">
@@ -9195,25 +8955,25 @@
         <v>200</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
@@ -9234,25 +8994,25 @@
         <v>400</v>
       </c>
       <c r="E59" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="G59" t="n">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="H59" t="n">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="I59" t="n">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="J59" t="n">
-        <v>496</v>
+        <v>646</v>
       </c>
       <c r="K59" t="n">
-        <v>496</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60">
@@ -9273,25 +9033,25 @@
         <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="G60" t="n">
-        <v>645</v>
+        <v>495</v>
       </c>
       <c r="H60" t="n">
-        <v>645</v>
+        <v>495</v>
       </c>
       <c r="I60" t="n">
-        <v>645</v>
+        <v>495</v>
       </c>
       <c r="J60" t="n">
-        <v>645</v>
+        <v>695</v>
       </c>
       <c r="K60" t="n">
-        <v>645</v>
+        <v>695</v>
       </c>
     </row>
     <row r="61">
@@ -9312,25 +9072,25 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="G61" t="n">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="H61" t="n">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="I61" t="n">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="J61" t="n">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="K61" t="n">
-        <v>178</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62">
@@ -9351,25 +9111,25 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>605</v>
+        <v>705</v>
       </c>
       <c r="G62" t="n">
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="H62" t="n">
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="I62" t="n">
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="J62" t="n">
-        <v>505</v>
+        <v>705</v>
       </c>
       <c r="K62" t="n">
-        <v>505</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63">
@@ -9390,25 +9150,25 @@
         <v>339</v>
       </c>
       <c r="E63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>417</v>
+        <v>178</v>
       </c>
       <c r="G63" t="n">
-        <v>417</v>
+        <v>178</v>
       </c>
       <c r="H63" t="n">
-        <v>417</v>
+        <v>178</v>
       </c>
       <c r="I63" t="n">
-        <v>417</v>
+        <v>517</v>
       </c>
       <c r="J63" t="n">
-        <v>417</v>
+        <v>517</v>
       </c>
       <c r="K63" t="n">
-        <v>417</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -9605,7 +9365,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G5" t="n">
         <v>124</v>
@@ -9761,7 +9521,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G9" t="n">
         <v>111</v>
@@ -9800,10 +9560,10 @@
         <v>118</v>
       </c>
       <c r="F10" t="n">
+        <v>172</v>
+      </c>
+      <c r="G10" t="n">
         <v>54</v>
-      </c>
-      <c r="G10" t="n">
-        <v>149</v>
       </c>
       <c r="H10" t="n">
         <v>149</v>
@@ -9839,7 +9599,7 @@
         <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
         <v>109</v>
@@ -9878,7 +9638,7 @@
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="G12" t="n">
         <v>104</v>
@@ -9890,7 +9650,7 @@
         <v>104</v>
       </c>
       <c r="J12" t="n">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
         <v>152</v>
@@ -9956,7 +9716,7 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -9968,7 +9728,7 @@
         <v>93</v>
       </c>
       <c r="J14" t="n">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="K14" t="n">
         <v>189</v>
@@ -9998,13 +9758,13 @@
         <v>164</v>
       </c>
       <c r="G15" t="n">
+        <v>164</v>
+      </c>
+      <c r="H15" t="n">
         <v>109</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>205</v>
-      </c>
-      <c r="I15" t="n">
-        <v>253</v>
       </c>
       <c r="J15" t="n">
         <v>253</v>
@@ -10073,13 +9833,13 @@
         <v>195</v>
       </c>
       <c r="F17" t="n">
+        <v>65</v>
+      </c>
+      <c r="G17" t="n">
         <v>112</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>60</v>
-      </c>
-      <c r="H17" t="n">
-        <v>156</v>
       </c>
       <c r="I17" t="n">
         <v>156</v>
@@ -10124,7 +9884,7 @@
         <v>103</v>
       </c>
       <c r="J18" t="n">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="K18" t="n">
         <v>151</v>
@@ -10154,7 +9914,7 @@
         <v>134</v>
       </c>
       <c r="G19" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H19" t="n">
         <v>104</v>
@@ -10163,7 +9923,7 @@
         <v>104</v>
       </c>
       <c r="J19" t="n">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="K19" t="n">
         <v>152</v>
@@ -10193,13 +9953,13 @@
         <v>107</v>
       </c>
       <c r="G20" t="n">
+        <v>107</v>
+      </c>
+      <c r="H20" t="n">
         <v>123</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>87</v>
-      </c>
-      <c r="I20" t="n">
-        <v>183</v>
       </c>
       <c r="J20" t="n">
         <v>183</v>
@@ -10235,7 +9995,7 @@
         <v>105</v>
       </c>
       <c r="H21" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I21" t="n">
         <v>111</v>
@@ -10268,7 +10028,7 @@
         <v>360</v>
       </c>
       <c r="F22" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
         <v>99</v>
@@ -10277,10 +10037,10 @@
         <v>99</v>
       </c>
       <c r="I22" t="n">
+        <v>99</v>
+      </c>
+      <c r="J22" t="n">
         <v>87</v>
-      </c>
-      <c r="J22" t="n">
-        <v>171</v>
       </c>
       <c r="K22" t="n">
         <v>171</v>
@@ -10349,10 +10109,10 @@
         <v>98</v>
       </c>
       <c r="G24" t="n">
+        <v>98</v>
+      </c>
+      <c r="H24" t="n">
         <v>146</v>
-      </c>
-      <c r="H24" t="n">
-        <v>116</v>
       </c>
       <c r="I24" t="n">
         <v>116</v>
@@ -10385,13 +10145,13 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G25" t="n">
         <v>142</v>
       </c>
       <c r="H25" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="I25" t="n">
         <v>112</v>
@@ -10430,7 +10190,7 @@
         <v>132</v>
       </c>
       <c r="H26" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I26" t="n">
         <v>102</v>
@@ -10463,19 +10223,19 @@
         <v>390</v>
       </c>
       <c r="F27" t="n">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="G27" t="n">
         <v>221</v>
       </c>
       <c r="H27" t="n">
+        <v>221</v>
+      </c>
+      <c r="I27" t="n">
         <v>131</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>77</v>
-      </c>
-      <c r="J27" t="n">
-        <v>101</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -10596,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
         <v>142</v>
@@ -10632,16 +10392,16 @@
         <v>250</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
         <v>99</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>69</v>
-      </c>
-      <c r="H4" t="n">
-        <v>199</v>
       </c>
       <c r="I4" t="n">
         <v>199</v>
@@ -10674,13 +10434,13 @@
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>103</v>
       </c>
       <c r="H5" t="n">
-        <v>233</v>
+        <v>103</v>
       </c>
       <c r="I5" t="n">
         <v>233</v>
@@ -10752,10 +10512,10 @@
         <v>30</v>
       </c>
       <c r="F7" t="n">
+        <v>96</v>
+      </c>
+      <c r="G7" t="n">
         <v>66</v>
-      </c>
-      <c r="G7" t="n">
-        <v>196</v>
       </c>
       <c r="H7" t="n">
         <v>196</v>
@@ -10791,10 +10551,10 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
+        <v>124</v>
+      </c>
+      <c r="G8" t="n">
         <v>109</v>
-      </c>
-      <c r="G8" t="n">
-        <v>94</v>
       </c>
       <c r="H8" t="n">
         <v>94</v>
@@ -10833,7 +10593,7 @@
         <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>176</v>
+        <v>61</v>
       </c>
       <c r="H9" t="n">
         <v>176</v>
@@ -10869,10 +10629,10 @@
         <v>120</v>
       </c>
       <c r="F10" t="n">
+        <v>135</v>
+      </c>
+      <c r="G10" t="n">
         <v>105</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -10911,7 +10671,7 @@
         <v>144</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="H11" t="n">
         <v>114</v>
@@ -10947,13 +10707,13 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
         <v>61</v>
       </c>
       <c r="H12" t="n">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="I12" t="n">
         <v>191</v>
@@ -10989,7 +10749,7 @@
         <v>110</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
         <v>20</v>
@@ -11022,13 +10782,13 @@
         <v>130</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
+        <v>89</v>
+      </c>
+      <c r="G14" t="n">
         <v>75</v>
-      </c>
-      <c r="G14" t="n">
-        <v>205</v>
       </c>
       <c r="H14" t="n">
         <v>205</v>
@@ -11275,19 +11035,19 @@
         <v>507</v>
       </c>
       <c r="F3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>86</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>226</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>41</v>
-      </c>
-      <c r="J3" t="n">
-        <v>361</v>
       </c>
       <c r="K3" t="n">
         <v>361</v>
@@ -11314,19 +11074,19 @@
         <v>907</v>
       </c>
       <c r="F4" t="n">
+        <v>773</v>
+      </c>
+      <c r="G4" t="n">
         <v>696</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>631</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>526</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>426</v>
-      </c>
-      <c r="J4" t="n">
-        <v>776</v>
       </c>
       <c r="K4" t="n">
         <v>776</v>
@@ -11353,10 +11113,10 @@
         <v>225</v>
       </c>
       <c r="F5" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G5" t="n">
         <v>1227</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1212</v>
       </c>
       <c r="H5" t="n">
         <v>1212</v>
@@ -11365,7 +11125,7 @@
         <v>1212</v>
       </c>
       <c r="J5" t="n">
-        <v>1062</v>
+        <v>1212</v>
       </c>
       <c r="K5" t="n">
         <v>1062</v>
@@ -11392,19 +11152,19 @@
         <v>485</v>
       </c>
       <c r="F6" t="n">
+        <v>691</v>
+      </c>
+      <c r="G6" t="n">
         <v>656</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>431</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>536</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>711</v>
-      </c>
-      <c r="J6" t="n">
-        <v>801</v>
       </c>
       <c r="K6" t="n">
         <v>801</v>
@@ -11431,16 +11191,16 @@
         <v>382</v>
       </c>
       <c r="F7" t="n">
+        <v>1217</v>
+      </c>
+      <c r="G7" t="n">
         <v>1072</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1045</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>835</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1010</v>
       </c>
       <c r="J7" t="n">
         <v>1010</v>
@@ -11470,19 +11230,19 @@
         <v>750</v>
       </c>
       <c r="F8" t="n">
+        <v>569</v>
+      </c>
+      <c r="G8" t="n">
         <v>339</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>654</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1034</v>
       </c>
       <c r="I8" t="n">
         <v>1034</v>
       </c>
       <c r="J8" t="n">
-        <v>974</v>
+        <v>1034</v>
       </c>
       <c r="K8" t="n">
         <v>974</v>
@@ -11509,16 +11269,16 @@
         <v>510</v>
       </c>
       <c r="F9" t="n">
+        <v>1462</v>
+      </c>
+      <c r="G9" t="n">
         <v>1402</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1342</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1042</v>
-      </c>
-      <c r="I9" t="n">
-        <v>987</v>
       </c>
       <c r="J9" t="n">
         <v>987</v>
@@ -11630,25 +11390,25 @@
         <v>1080</v>
       </c>
       <c r="E13" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="H13" t="n">
-        <v>-4</v>
+        <v>261</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>381</v>
       </c>
       <c r="J13" t="n">
-        <v>426</v>
+        <v>741</v>
       </c>
       <c r="K13" t="n">
-        <v>426</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="14">
@@ -11669,25 +11429,25 @@
         <v>900</v>
       </c>
       <c r="E14" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>475</v>
       </c>
       <c r="G14" t="n">
-        <v>265</v>
+        <v>475</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>475</v>
       </c>
       <c r="I14" t="n">
-        <v>105</v>
+        <v>595</v>
       </c>
       <c r="J14" t="n">
-        <v>465</v>
+        <v>1015</v>
       </c>
       <c r="K14" t="n">
-        <v>465</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="15">
@@ -11711,13 +11471,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>265</v>
+      </c>
+      <c r="G15" t="n">
         <v>325</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>381</v>
-      </c>
-      <c r="H15" t="n">
-        <v>441</v>
       </c>
       <c r="I15" t="n">
         <v>441</v>
@@ -11747,25 +11507,25 @@
         <v>840</v>
       </c>
       <c r="E16" t="n">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-33</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="H16" t="n">
-        <v>47</v>
+        <v>312</v>
       </c>
       <c r="I16" t="n">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="J16" t="n">
-        <v>317</v>
+        <v>672</v>
       </c>
       <c r="K16" t="n">
-        <v>317</v>
+        <v>912</v>
       </c>
     </row>
     <row r="17">
@@ -11786,25 +11546,25 @@
         <v>354</v>
       </c>
       <c r="E17" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>307</v>
+        <v>133</v>
       </c>
       <c r="G17" t="n">
         <v>307</v>
       </c>
       <c r="H17" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I17" t="n">
-        <v>312</v>
+        <v>487</v>
       </c>
       <c r="J17" t="n">
-        <v>312</v>
+        <v>487</v>
       </c>
       <c r="K17" t="n">
-        <v>312</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18">
@@ -11825,25 +11585,25 @@
         <v>1125</v>
       </c>
       <c r="E18" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-24</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>431</v>
       </c>
       <c r="H18" t="n">
-        <v>242</v>
+        <v>1017</v>
       </c>
       <c r="I18" t="n">
-        <v>242</v>
+        <v>1257</v>
       </c>
       <c r="J18" t="n">
-        <v>242</v>
+        <v>1257</v>
       </c>
       <c r="K18" t="n">
-        <v>242</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="19">
@@ -11864,7 +11624,7 @@
         <v>180</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>106</v>
@@ -11873,16 +11633,16 @@
         <v>106</v>
       </c>
       <c r="H19" t="n">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="I19" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="J19" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="K19" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20">
@@ -12085,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>20</v>
@@ -12124,7 +11884,7 @@
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
@@ -12199,13 +11959,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>50</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -12244,7 +12004,7 @@
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
         <v>35</v>
@@ -12280,10 +12040,10 @@
         <v>25</v>
       </c>
       <c r="H8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
         <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>85</v>
       </c>
       <c r="J8" t="n">
         <v>85</v>
